--- a/database/event/3494/event_3494_evp_summary.xlsx
+++ b/database/event/3494/event_3494_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6364</v>
+        <v>7.0185</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2288</v>
+        <v>1.2995</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2596</v>
+        <v>2.3523</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6364</v>
+        <v>7.0185</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0329</v>
+        <v>4.415</v>
       </c>
       <c r="G2" t="n">
         <v>2.6035</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0329</v>
+        <v>5.202</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2688</v>
+        <v>4.2164</v>
       </c>
       <c r="J2" t="n">
         <v>2.6035</v>
@@ -529,7 +529,7 @@
         <v>131</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8723</v>
+        <v>6.819900000000001</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2284</v>
+        <v>6.6296</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1532</v>
+        <v>1.2275</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0948</v>
+        <v>2.1973</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2284</v>
+        <v>6.6296</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2503</v>
+        <v>4.6515</v>
       </c>
       <c r="G3" t="n">
         <v>1.9781</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5393</v>
+        <v>6.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6792</v>
+        <v>4.9877</v>
       </c>
       <c r="J3" t="n">
         <v>1.9781</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>5.657299999999999</v>
+        <v>6.9658</v>
       </c>
       <c r="N3" t="n">
         <v>274</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3221</v>
+        <v>5.695</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9854000000000001</v>
+        <v>1.0545</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7286</v>
+        <v>1.825</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3221</v>
+        <v>5.695</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2695</v>
+        <v>4.6424</v>
       </c>
       <c r="G4" t="n">
         <v>1.0526</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6169</v>
+        <v>6.1169</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7421</v>
+        <v>4.9579</v>
       </c>
       <c r="J4" t="n">
         <v>1.0526</v>
@@ -621,7 +621,7 @@
         <v>59</v>
       </c>
       <c r="M4" t="n">
-        <v>4.794700000000001</v>
+        <v>6.0105</v>
       </c>
       <c r="N4" t="n">
         <v>209</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2856</v>
+        <v>5.5051</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9787</v>
+        <v>1.0193</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7139</v>
+        <v>1.7493</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2856</v>
+        <v>5.5051</v>
       </c>
       <c r="F5" t="n">
-        <v>4.159</v>
+        <v>4.3785</v>
       </c>
       <c r="G5" t="n">
         <v>1.1266</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1723</v>
+        <v>5.0551</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3818</v>
+        <v>4.0973</v>
       </c>
       <c r="J5" t="n">
         <v>1.1266</v>
@@ -667,7 +667,7 @@
         <v>128</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5084</v>
+        <v>5.2239</v>
       </c>
       <c r="N5" t="n">
         <v>274</v>
@@ -676,219 +676,219 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5845</v>
+        <v>4.8659</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8489</v>
+        <v>0.901</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4307</v>
+        <v>1.4947</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5845</v>
+        <v>4.8659</v>
       </c>
       <c r="F6" t="n">
-        <v>4.218</v>
+        <v>4.774</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3665</v>
+        <v>0.0919</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4097</v>
+        <v>6.6464</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5741</v>
+        <v>5.3871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3665</v>
+        <v>0.0919</v>
       </c>
       <c r="K6" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="L6" t="n">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9406</v>
+        <v>5.479</v>
       </c>
       <c r="N6" t="n">
-        <v>200</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5323</v>
+        <v>4.7311</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.876</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4096</v>
+        <v>1.441</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5323</v>
+        <v>4.7311</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4404</v>
+        <v>4.3646</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0919</v>
+        <v>0.3665</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3041</v>
+        <v>4.9992</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2991</v>
+        <v>4.052</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0919</v>
+        <v>0.3665</v>
       </c>
       <c r="K7" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="L7" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>4.391</v>
+        <v>4.4185</v>
       </c>
       <c r="N7" t="n">
-        <v>284</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7087</v>
+        <v>4.4295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6867</v>
+        <v>0.8202</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0769</v>
+        <v>1.3208</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7087</v>
+        <v>4.4295</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8514</v>
+        <v>3.7988</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8573</v>
+        <v>0.6307</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8514</v>
+        <v>3.7988</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3112</v>
+        <v>3.079</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8573</v>
+        <v>0.6307</v>
       </c>
       <c r="K8" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="L8" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1685</v>
+        <v>3.7097</v>
       </c>
       <c r="N8" t="n">
-        <v>284</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6967</v>
+        <v>4.3788</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6845</v>
+        <v>0.8108</v>
       </c>
       <c r="D9" t="n">
-        <v>1.072</v>
+        <v>1.3006</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6967</v>
+        <v>4.3788</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5245</v>
+        <v>3.5215</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1722</v>
+        <v>0.8573</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5245</v>
+        <v>3.5215</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8567</v>
+        <v>2.8543</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1722</v>
+        <v>0.8573</v>
       </c>
       <c r="K9" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="L9" t="n">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0289</v>
+        <v>3.7116</v>
       </c>
       <c r="N9" t="n">
-        <v>200</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6937</v>
+        <v>4.1485</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6839</v>
+        <v>0.7681</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0708</v>
+        <v>1.2089</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6937</v>
+        <v>4.1485</v>
       </c>
       <c r="F10" t="n">
-        <v>3.063</v>
+        <v>3.9763</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6307</v>
+        <v>0.1722</v>
       </c>
       <c r="H10" t="n">
-        <v>3.063</v>
+        <v>3.9763</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4826</v>
+        <v>3.2229</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6307</v>
+        <v>0.1722</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1133</v>
+        <v>3.3951</v>
       </c>
       <c r="N10" t="n">
         <v>200</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2052</v>
+        <v>3.8222</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5935</v>
+        <v>0.7077</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8735000000000001</v>
+        <v>1.0789</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2052</v>
+        <v>3.8222</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1645</v>
+        <v>3.7815</v>
       </c>
       <c r="G11" t="n">
         <v>0.0407</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1645</v>
+        <v>3.7815</v>
       </c>
       <c r="I11" t="n">
-        <v>2.565</v>
+        <v>3.065</v>
       </c>
       <c r="J11" t="n">
         <v>0.0407</v>
@@ -943,7 +943,7 @@
         <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6057</v>
+        <v>3.1057</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8004</v>
+        <v>2.8776</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5185</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7099</v>
+        <v>0.7025</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8004</v>
+        <v>2.8776</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4897</v>
+        <v>3.5669</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6893</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4897</v>
+        <v>3.5669</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8285</v>
+        <v>2.8911</v>
       </c>
       <c r="J12" t="n">
         <v>-0.6893</v>
@@ -989,7 +989,7 @@
         <v>56</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1392</v>
+        <v>2.2018</v>
       </c>
       <c r="N12" t="n">
         <v>200</v>
@@ -998,415 +998,415 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2055</v>
+        <v>2.5436</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4084</v>
+        <v>0.471</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4696</v>
+        <v>0.5695</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2055</v>
+        <v>2.5436</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4658</v>
+        <v>2.5436</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2603</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4658</v>
+        <v>2.5436</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9986</v>
+        <v>2.5436</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2603</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L13" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7383</v>
+        <v>2.5436</v>
       </c>
       <c r="N13" t="n">
-        <v>274</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9451</v>
+        <v>2.398</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3602</v>
+        <v>0.444</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3644</v>
+        <v>0.5115</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9451</v>
+        <v>2.398</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9451</v>
+        <v>2.6583</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.2603</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9451</v>
+        <v>2.6583</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9451</v>
+        <v>2.1546</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.2603</v>
       </c>
       <c r="K14" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9451</v>
+        <v>1.8943</v>
       </c>
       <c r="N14" t="n">
-        <v>147</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>fleav</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5897</v>
+        <v>2.166</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2943</v>
+        <v>0.4011</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2208</v>
+        <v>0.419</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5897</v>
+        <v>2.166</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2249</v>
+        <v>2.166</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3648</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2249</v>
+        <v>2.166</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9928</v>
+        <v>2.166</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3648</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="L15" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3576</v>
+        <v>2.166</v>
       </c>
       <c r="N15" t="n">
-        <v>284</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>kolor</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5598</v>
+        <v>2.1412</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2888</v>
+        <v>0.3965</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2088</v>
+        <v>0.4091</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5598</v>
+        <v>2.1412</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0589</v>
+        <v>2.1412</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4991</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0589</v>
+        <v>2.1412</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6688</v>
+        <v>2.1412</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4991</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="L16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1697</v>
+        <v>2.1412</v>
       </c>
       <c r="N16" t="n">
-        <v>209</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.505</v>
+        <v>2.0504</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2787</v>
+        <v>0.3796</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1866</v>
+        <v>0.373</v>
       </c>
       <c r="E17" t="n">
-        <v>1.505</v>
+        <v>2.0504</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0818</v>
+        <v>2.5495</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4232</v>
+        <v>-0.4991</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0818</v>
+        <v>2.5495</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0663</v>
+        <v>2.0664</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4232</v>
+        <v>-0.4991</v>
       </c>
       <c r="K17" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="L17" t="n">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4895</v>
+        <v>1.5673</v>
       </c>
       <c r="N17" t="n">
-        <v>274</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DEV7L</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4633</v>
+        <v>1.6912</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2709</v>
+        <v>0.3131</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1698</v>
+        <v>0.2299</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4633</v>
+        <v>1.6912</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4633</v>
+        <v>0.268</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.4232</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4633</v>
+        <v>0.268</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4633</v>
+        <v>0.2172</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.4232</v>
       </c>
       <c r="K18" t="n">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4633</v>
+        <v>1.6404</v>
       </c>
       <c r="N18" t="n">
-        <v>167</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fleav</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3565</v>
+        <v>1.6538</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2512</v>
+        <v>0.3062</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1266</v>
+        <v>0.215</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3565</v>
+        <v>1.6538</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3565</v>
+        <v>1.289</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3648</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3565</v>
+        <v>1.289</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3565</v>
+        <v>1.0448</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3648</v>
       </c>
       <c r="K19" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3565</v>
+        <v>1.4096</v>
       </c>
       <c r="N19" t="n">
-        <v>147</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kolor</t>
+          <t>DEV7L</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2819</v>
+        <v>1.648</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2374</v>
+        <v>0.3051</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0965</v>
+        <v>0.2127</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2819</v>
+        <v>1.648</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2819</v>
+        <v>1.648</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2819</v>
+        <v>1.648</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2819</v>
+        <v>1.648</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2819</v>
+        <v>1.648</v>
       </c>
       <c r="N20" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>queztone</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9448</v>
+        <v>1.2454</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1749</v>
+        <v>0.2306</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0397</v>
+        <v>0.0523</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9448</v>
+        <v>1.2454</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9946</v>
+        <v>1.2454</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9394</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9946</v>
+        <v>1.2454</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8062</v>
+        <v>1.2454</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9394</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L21" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1332</v>
+        <v>1.2454</v>
       </c>
       <c r="N21" t="n">
-        <v>284</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9132</v>
+        <v>1.1736</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1691</v>
+        <v>0.2173</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0524</v>
+        <v>0.0237</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9132</v>
+        <v>1.1736</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0881</v>
+        <v>1.3485</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1749</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0881</v>
+        <v>1.3485</v>
       </c>
       <c r="I22" t="n">
-        <v>0.882</v>
+        <v>1.093</v>
       </c>
       <c r="J22" t="n">
         <v>-0.1749</v>
@@ -1449,7 +1449,7 @@
         <v>56</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7071000000000001</v>
+        <v>0.9180999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>200</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>queztone</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8434</v>
+        <v>1.1349</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1562</v>
+        <v>0.2101</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0806</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8434</v>
+        <v>1.1349</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8434</v>
+        <v>-0.8045</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1.9394</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8434</v>
+        <v>-0.8045</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8434</v>
+        <v>-0.6521</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.9394</v>
       </c>
       <c r="K23" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8434</v>
+        <v>1.2873</v>
       </c>
       <c r="N23" t="n">
-        <v>167</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6044</v>
+        <v>0.7113</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1119</v>
+        <v>0.1317</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1772</v>
+        <v>-0.1605</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6044</v>
+        <v>0.7113</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6044</v>
+        <v>0.7113</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6044</v>
+        <v>0.7113</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6044</v>
+        <v>0.7113</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6044</v>
+        <v>0.7113</v>
       </c>
       <c r="N24" t="n">
         <v>167</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3543</v>
+        <v>0.5877</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.1088</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2782</v>
+        <v>-0.2098</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3543</v>
+        <v>0.5877</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3543</v>
+        <v>0.5877</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3543</v>
+        <v>0.5877</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3543</v>
+        <v>0.5877</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3543</v>
+        <v>0.5877</v>
       </c>
       <c r="N25" t="n">
         <v>167</v>
@@ -1596,369 +1596,369 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3156</v>
+        <v>0.4407</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0584</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2939</v>
+        <v>-0.2683</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3156</v>
+        <v>0.4407</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9477</v>
+        <v>0.4407</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6321</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9477</v>
+        <v>0.4407</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7681</v>
+        <v>0.4407</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6321</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L26" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.136</v>
+        <v>0.4407</v>
       </c>
       <c r="N26" t="n">
-        <v>209</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2967</v>
+        <v>0.434</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0549</v>
+        <v>0.0804</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3015</v>
+        <v>-0.271</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2967</v>
+        <v>0.434</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2967</v>
+        <v>1.0661</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.6321</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2967</v>
+        <v>1.0661</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2967</v>
+        <v>0.8641</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.6321</v>
       </c>
       <c r="K27" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2967</v>
+        <v>0.232</v>
       </c>
       <c r="N27" t="n">
-        <v>152</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ponczek</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5805</v>
+        <v>-0.1769</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1075</v>
+        <v>-0.0328</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6559</v>
+        <v>-0.5144</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5805</v>
+        <v>-0.1769</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5805</v>
+        <v>-0.1404</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.0365</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5805</v>
+        <v>-0.1404</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5805</v>
+        <v>-0.1138</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.0365</v>
       </c>
       <c r="K28" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.5805</v>
+        <v>-0.1503</v>
       </c>
       <c r="N28" t="n">
-        <v>152</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>ponczek</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6659</v>
+        <v>-0.5805</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1233</v>
+        <v>-0.1075</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6904</v>
+        <v>-0.6752</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6659</v>
+        <v>-0.5805</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0839</v>
+        <v>-0.5805</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.582</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0839</v>
+        <v>-0.5805</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.068</v>
+        <v>-0.5805</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.582</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L29" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6499999999999999</v>
+        <v>-0.5805</v>
       </c>
       <c r="N29" t="n">
-        <v>209</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MonttY</t>
+          <t>The eLiVe</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.722</v>
+        <v>-0.5849</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1337</v>
+        <v>-0.1083</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.713</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.722</v>
+        <v>-0.5849</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.722</v>
+        <v>-0.5849</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.722</v>
+        <v>-0.5849</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.722</v>
+        <v>-0.5849</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.722</v>
+        <v>-0.5849</v>
       </c>
       <c r="N30" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>beastik</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7368</v>
+        <v>-0.6659</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1364</v>
+        <v>-0.1233</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.719</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7368</v>
+        <v>-0.6659</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7368</v>
+        <v>-0.0839</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.582</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7368</v>
+        <v>-0.0839</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7368</v>
+        <v>-0.068</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.582</v>
       </c>
       <c r="K31" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7368</v>
+        <v>-0.6499999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>147</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>beastik</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.742</v>
+        <v>-0.6841</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1374</v>
+        <v>-0.1267</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7211</v>
+        <v>-0.7165</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.742</v>
+        <v>-0.6841</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7055</v>
+        <v>-0.6841</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0365</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7055</v>
+        <v>-0.6841</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5718</v>
+        <v>-0.6841</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0365</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L32" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6083</v>
+        <v>-0.6841</v>
       </c>
       <c r="N32" t="n">
-        <v>274</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>The eLiVe</t>
+          <t>MonttY</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9089</v>
+        <v>-0.722</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1683</v>
+        <v>-0.1337</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7885</v>
+        <v>-0.7316</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9089</v>
+        <v>-0.722</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9089</v>
+        <v>-0.722</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9089</v>
+        <v>-0.722</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9089</v>
+        <v>-0.722</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9089</v>
+        <v>-0.722</v>
       </c>
       <c r="N33" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34">
@@ -1974,7 +1974,7 @@
         <v>-0.1821</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8187</v>
+        <v>-0.8358</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9836</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3046</v>
+        <v>-1.2058</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2416</v>
+        <v>-0.2233</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9484</v>
+        <v>-0.9243</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3046</v>
+        <v>-1.2058</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3046</v>
+        <v>-1.2058</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3046</v>
+        <v>-1.2058</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3046</v>
+        <v>-1.2058</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.3046</v>
+        <v>-1.2058</v>
       </c>
       <c r="N35" t="n">
         <v>152</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2818</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0362</v>
+        <v>-1.0503</v>
       </c>
       <c r="E36" t="n">
         <v>-1.522</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2837</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0403</v>
+        <v>-1.0543</v>
       </c>
       <c r="E37" t="n">
         <v>-1.5321</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3368</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1561</v>
+        <v>-1.1685</v>
       </c>
       <c r="E38" t="n">
         <v>-1.8188</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.2676</v>
+        <v>-1.8559</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4199</v>
+        <v>-0.3436</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3374</v>
+        <v>-1.1833</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2676</v>
+        <v>-1.8559</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.2676</v>
+        <v>-1.8559</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.2676</v>
+        <v>-1.8559</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.2676</v>
+        <v>-1.8559</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.2676</v>
+        <v>-1.8559</v>
       </c>
       <c r="N39" t="n">
         <v>147</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4302</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.36</v>
+        <v>-1.3696</v>
       </c>
       <c r="E40" t="n">
         <v>-2.3236</v>
@@ -2296,7 +2296,7 @@
         <v>-0.4839</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4772</v>
+        <v>-1.4852</v>
       </c>
       <c r="E41" t="n">
         <v>-2.6137</v>

--- a/database/event/3494/event_3494_evp_summary.xlsx
+++ b/database/event/3494/event_3494_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0185</v>
+        <v>6.2312</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2995</v>
+        <v>1.1538</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3523</v>
+        <v>2.1751</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0185</v>
+        <v>6.2312</v>
       </c>
       <c r="F2" t="n">
-        <v>4.415</v>
+        <v>3.8189</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6035</v>
+        <v>2.4123</v>
       </c>
       <c r="H2" t="n">
-        <v>5.202</v>
+        <v>7.969</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2164</v>
+        <v>4.1435</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6035</v>
+        <v>2.4123</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>131</v>
       </c>
       <c r="M2" t="n">
-        <v>6.819900000000001</v>
+        <v>6.555800000000001</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6296</v>
+        <v>5.6428</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2275</v>
+        <v>1.0448</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1973</v>
+        <v>1.9094</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6296</v>
+        <v>5.6428</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6515</v>
+        <v>4.0847</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9781</v>
+        <v>1.5581</v>
       </c>
       <c r="H3" t="n">
-        <v>6.1536</v>
+        <v>8.9055</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9877</v>
+        <v>4.6305</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9781</v>
+        <v>1.5581</v>
       </c>
       <c r="K3" t="n">
         <v>146</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>6.9658</v>
+        <v>6.188599999999999</v>
       </c>
       <c r="N3" t="n">
         <v>274</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.695</v>
+        <v>5.1475</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0545</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.825</v>
+        <v>1.6858</v>
       </c>
       <c r="E4" t="n">
-        <v>5.695</v>
+        <v>5.1475</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6424</v>
+        <v>4.1373</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0526</v>
+        <v>1.0102</v>
       </c>
       <c r="H4" t="n">
-        <v>6.1169</v>
+        <v>9.0908</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9579</v>
+        <v>4.7268</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0526</v>
+        <v>1.0102</v>
       </c>
       <c r="K4" t="n">
         <v>150</v>
@@ -621,7 +621,7 @@
         <v>59</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0105</v>
+        <v>5.737</v>
       </c>
       <c r="N4" t="n">
         <v>209</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5051</v>
+        <v>4.9439</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0193</v>
+        <v>0.9154</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7493</v>
+        <v>1.5939</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5051</v>
+        <v>4.9439</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3785</v>
+        <v>3.7182</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1266</v>
+        <v>1.2257</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0551</v>
+        <v>7.6141</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0973</v>
+        <v>3.959</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1266</v>
+        <v>1.2257</v>
       </c>
       <c r="K5" t="n">
         <v>146</v>
@@ -667,7 +667,7 @@
         <v>128</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2239</v>
+        <v>5.1847</v>
       </c>
       <c r="N5" t="n">
         <v>274</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8659</v>
+        <v>4.5424</v>
       </c>
       <c r="C6" t="n">
-        <v>0.901</v>
+        <v>0.8411</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4947</v>
+        <v>1.4127</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8659</v>
+        <v>4.5424</v>
       </c>
       <c r="F6" t="n">
-        <v>4.774</v>
+        <v>4.31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0919</v>
+        <v>0.2324</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6464</v>
+        <v>9.6996</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3871</v>
+        <v>5.0433</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0919</v>
+        <v>0.2324</v>
       </c>
       <c r="K6" t="n">
         <v>153</v>
@@ -713,7 +713,7 @@
         <v>131</v>
       </c>
       <c r="M6" t="n">
-        <v>5.479</v>
+        <v>5.275700000000001</v>
       </c>
       <c r="N6" t="n">
         <v>284</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7311</v>
+        <v>4.2377</v>
       </c>
       <c r="C7" t="n">
-        <v>0.876</v>
+        <v>0.7846</v>
       </c>
       <c r="D7" t="n">
-        <v>1.441</v>
+        <v>1.2751</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7311</v>
+        <v>4.2377</v>
       </c>
       <c r="F7" t="n">
-        <v>4.3646</v>
+        <v>3.8076</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3665</v>
+        <v>0.4301</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9992</v>
+        <v>7.9294</v>
       </c>
       <c r="I7" t="n">
-        <v>4.052</v>
+        <v>4.1229</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3665</v>
+        <v>0.4301</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4185</v>
+        <v>4.553</v>
       </c>
       <c r="N7" t="n">
         <v>200</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4295</v>
+        <v>4.0832</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8202</v>
+        <v>0.756</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3208</v>
+        <v>1.2053</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4295</v>
+        <v>4.0832</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7988</v>
+        <v>3.1536</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6307</v>
+        <v>0.9296</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7988</v>
+        <v>5.6249</v>
       </c>
       <c r="I8" t="n">
-        <v>3.079</v>
+        <v>2.9247</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6307</v>
+        <v>0.9296</v>
       </c>
       <c r="K8" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="L8" t="n">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7097</v>
+        <v>3.8543</v>
       </c>
       <c r="N8" t="n">
-        <v>200</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3788</v>
+        <v>3.9506</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8108</v>
+        <v>0.7315</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3006</v>
+        <v>1.1455</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3788</v>
+        <v>3.9506</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5215</v>
+        <v>3.2889</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8573</v>
+        <v>0.6617</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5215</v>
+        <v>6.1017</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8543</v>
+        <v>3.1726</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8573</v>
+        <v>0.6617</v>
       </c>
       <c r="K9" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="L9" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7116</v>
+        <v>3.8343</v>
       </c>
       <c r="N9" t="n">
-        <v>284</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1485</v>
+        <v>3.7198</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7681</v>
+        <v>0.6888</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2089</v>
+        <v>1.0413</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1485</v>
+        <v>3.7198</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9763</v>
+        <v>3.431</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1722</v>
+        <v>0.2888</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9763</v>
+        <v>6.6025</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2229</v>
+        <v>3.433</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1722</v>
+        <v>0.2888</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3951</v>
+        <v>3.7218</v>
       </c>
       <c r="N10" t="n">
         <v>200</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8222</v>
+        <v>3.4162</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7077</v>
+        <v>0.6325</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0789</v>
+        <v>0.9042</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8222</v>
+        <v>3.4162</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7815</v>
+        <v>3.272</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0407</v>
+        <v>0.1442</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7815</v>
+        <v>6.0423</v>
       </c>
       <c r="I11" t="n">
-        <v>3.065</v>
+        <v>3.1417</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0407</v>
+        <v>0.1442</v>
       </c>
       <c r="K11" t="n">
         <v>150</v>
@@ -943,7 +943,7 @@
         <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1057</v>
+        <v>3.2859</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -952,216 +952,216 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8776</v>
+        <v>3.0805</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5704</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7025</v>
+        <v>0.7527</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8776</v>
+        <v>3.0805</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5669</v>
+        <v>2.9947</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6893</v>
+        <v>0.0858</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5669</v>
+        <v>5.0653</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8911</v>
+        <v>2.6337</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6893</v>
+        <v>0.0858</v>
       </c>
       <c r="K12" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L12" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2018</v>
+        <v>2.7195</v>
       </c>
       <c r="N12" t="n">
-        <v>200</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5436</v>
+        <v>2.9983</v>
       </c>
       <c r="C13" t="n">
-        <v>0.471</v>
+        <v>0.5552</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5695</v>
+        <v>0.7156</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5436</v>
+        <v>2.9983</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5436</v>
+        <v>1.6484</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.3499</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5436</v>
+        <v>1.6484</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5436</v>
+        <v>0.8571</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.3499</v>
       </c>
       <c r="K13" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5436</v>
+        <v>2.207</v>
       </c>
       <c r="N13" t="n">
-        <v>147</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.398</v>
+        <v>2.9205</v>
       </c>
       <c r="C14" t="n">
-        <v>0.444</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5115</v>
+        <v>0.6804</v>
       </c>
       <c r="E14" t="n">
-        <v>2.398</v>
+        <v>2.9205</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6583</v>
+        <v>3.346</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2603</v>
+        <v>-0.4255</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6583</v>
+        <v>6.3029</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1546</v>
+        <v>3.2772</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2603</v>
+        <v>-0.4255</v>
       </c>
       <c r="K14" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L14" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8943</v>
+        <v>2.8517</v>
       </c>
       <c r="N14" t="n">
-        <v>274</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fleav</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.166</v>
+        <v>2.7823</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4011</v>
+        <v>0.5152</v>
       </c>
       <c r="D15" t="n">
-        <v>0.419</v>
+        <v>0.6181</v>
       </c>
       <c r="E15" t="n">
-        <v>2.166</v>
+        <v>2.7823</v>
       </c>
       <c r="F15" t="n">
-        <v>2.166</v>
+        <v>2.3245</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.4578</v>
       </c>
       <c r="H15" t="n">
-        <v>2.166</v>
+        <v>2.7037</v>
       </c>
       <c r="I15" t="n">
-        <v>2.166</v>
+        <v>1.4058</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.4578</v>
       </c>
       <c r="K15" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M15" t="n">
-        <v>2.166</v>
+        <v>1.8636</v>
       </c>
       <c r="N15" t="n">
-        <v>147</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kolor</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1412</v>
+        <v>2.6099</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3965</v>
+        <v>0.4832</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4091</v>
+        <v>0.5402</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1412</v>
+        <v>2.6099</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1412</v>
+        <v>2.6099</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1412</v>
+        <v>2.6099</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1412</v>
+        <v>2.6099</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1412</v>
+        <v>2.6099</v>
       </c>
       <c r="N16" t="n">
         <v>147</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0504</v>
+        <v>2.4638</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3796</v>
+        <v>0.4562</v>
       </c>
       <c r="D17" t="n">
-        <v>0.373</v>
+        <v>0.4743</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0504</v>
+        <v>2.4638</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5495</v>
+        <v>2.7706</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4991</v>
+        <v>-0.3068</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5495</v>
+        <v>4.2756</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0664</v>
+        <v>2.2231</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4991</v>
+        <v>-0.3068</v>
       </c>
       <c r="K17" t="n">
         <v>150</v>
@@ -1219,7 +1219,7 @@
         <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5673</v>
+        <v>1.9163</v>
       </c>
       <c r="N17" t="n">
         <v>209</v>
@@ -1228,170 +1228,170 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6912</v>
+        <v>2.4093</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3131</v>
+        <v>0.4461</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2299</v>
+        <v>0.4497</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6912</v>
+        <v>2.4093</v>
       </c>
       <c r="F18" t="n">
-        <v>0.268</v>
+        <v>2.4223</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4232</v>
+        <v>-0.013</v>
       </c>
       <c r="H18" t="n">
-        <v>0.268</v>
+        <v>3.0485</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2172</v>
+        <v>1.5851</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4232</v>
+        <v>-0.013</v>
       </c>
       <c r="K18" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L18" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6404</v>
+        <v>1.5721</v>
       </c>
       <c r="N18" t="n">
-        <v>274</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>fleav</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6538</v>
+        <v>2.2775</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3062</v>
+        <v>0.4217</v>
       </c>
       <c r="D19" t="n">
-        <v>0.215</v>
+        <v>0.3902</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6538</v>
+        <v>2.2775</v>
       </c>
       <c r="F19" t="n">
-        <v>1.289</v>
+        <v>2.2775</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3648</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.289</v>
+        <v>2.2775</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0448</v>
+        <v>2.2775</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3648</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="L19" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4096</v>
+        <v>2.2775</v>
       </c>
       <c r="N19" t="n">
-        <v>284</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DEV7L</t>
+          <t>kolor</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.648</v>
+        <v>2.2229</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3051</v>
+        <v>0.4116</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2127</v>
+        <v>0.3655</v>
       </c>
       <c r="E20" t="n">
-        <v>1.648</v>
+        <v>2.2229</v>
       </c>
       <c r="F20" t="n">
-        <v>1.648</v>
+        <v>2.2229</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.648</v>
+        <v>2.2229</v>
       </c>
       <c r="I20" t="n">
-        <v>1.648</v>
+        <v>2.2229</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.648</v>
+        <v>2.2229</v>
       </c>
       <c r="N20" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>queztone</t>
+          <t>DEV7L</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2454</v>
+        <v>1.9474</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2306</v>
+        <v>0.3606</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0523</v>
+        <v>0.2411</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2454</v>
+        <v>1.9474</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2454</v>
+        <v>1.9474</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2454</v>
+        <v>1.9474</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2454</v>
+        <v>1.9474</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2454</v>
+        <v>1.9474</v>
       </c>
       <c r="N21" t="n">
         <v>167</v>
@@ -1412,170 +1412,170 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1736</v>
+        <v>1.8737</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2173</v>
+        <v>0.3469</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0237</v>
+        <v>0.2079</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1736</v>
+        <v>1.8737</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3485</v>
+        <v>2.2716</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1749</v>
+        <v>-0.3979</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3485</v>
+        <v>2.5173</v>
       </c>
       <c r="I22" t="n">
-        <v>1.093</v>
+        <v>1.3089</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1749</v>
+        <v>-0.3979</v>
       </c>
       <c r="K22" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="L22" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9180999999999999</v>
+        <v>0.911</v>
       </c>
       <c r="N22" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>queztone</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1349</v>
+        <v>1.6383</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2101</v>
+        <v>0.3033</v>
       </c>
       <c r="D23" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1016</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1349</v>
+        <v>1.6383</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8045</v>
+        <v>1.6383</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9394</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8045</v>
+        <v>1.6383</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6521</v>
+        <v>1.6383</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9394</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L23" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2873</v>
+        <v>1.6383</v>
       </c>
       <c r="N23" t="n">
-        <v>284</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7113</v>
+        <v>1.6027</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1317</v>
+        <v>0.2968</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1605</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7113</v>
+        <v>1.6027</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7113</v>
+        <v>-0.1531</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.7558</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7113</v>
+        <v>-0.1531</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7113</v>
+        <v>-0.0796</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.7558</v>
       </c>
       <c r="K24" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7113</v>
+        <v>1.6762</v>
       </c>
       <c r="N24" t="n">
-        <v>167</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZEDKO</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5877</v>
+        <v>1.399</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1088</v>
+        <v>0.259</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2098</v>
+        <v>-0.0064</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5877</v>
+        <v>1.399</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5877</v>
+        <v>1.399</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5877</v>
+        <v>1.399</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5877</v>
+        <v>1.399</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5877</v>
+        <v>1.399</v>
       </c>
       <c r="N25" t="n">
         <v>167</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>ZEDKO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4407</v>
+        <v>1.0895</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.2017</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2683</v>
+        <v>-0.1462</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4407</v>
+        <v>1.0895</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4407</v>
+        <v>1.0895</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4407</v>
+        <v>1.0895</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4407</v>
+        <v>1.0895</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4407</v>
+        <v>1.0895</v>
       </c>
       <c r="N26" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.434</v>
+        <v>0.7226</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0804</v>
+        <v>0.1338</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.271</v>
+        <v>-0.3118</v>
       </c>
       <c r="E27" t="n">
-        <v>0.434</v>
+        <v>0.7226</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0661</v>
+        <v>0.7226</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6321</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0661</v>
+        <v>0.7226</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8641</v>
+        <v>0.7226</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.6321</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L27" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.232</v>
+        <v>0.7226</v>
       </c>
       <c r="N27" t="n">
-        <v>209</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1769</v>
+        <v>0.6748</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0328</v>
+        <v>0.1249</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5144</v>
+        <v>-0.3334</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1769</v>
+        <v>0.6748</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1404</v>
+        <v>0.4317</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0365</v>
+        <v>0.2431</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1404</v>
+        <v>0.4317</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1138</v>
+        <v>0.2245</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0365</v>
+        <v>0.2431</v>
       </c>
       <c r="K28" t="n">
         <v>146</v>
@@ -1725,7 +1725,7 @@
         <v>128</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1503</v>
+        <v>0.4676</v>
       </c>
       <c r="N28" t="n">
         <v>274</v>
@@ -1734,78 +1734,78 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ponczek</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5805</v>
+        <v>0.445</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1075</v>
+        <v>0.0824</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6752</v>
+        <v>-0.4371</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5805</v>
+        <v>0.445</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5805</v>
+        <v>0.8037</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.3587</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5805</v>
+        <v>0.8037</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5805</v>
+        <v>0.4179</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.3587</v>
       </c>
       <c r="K29" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5805</v>
+        <v>0.05919999999999997</v>
       </c>
       <c r="N29" t="n">
-        <v>152</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>The eLiVe</t>
+          <t>beastik</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5849</v>
+        <v>0.1572</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1083</v>
+        <v>0.0291</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5849</v>
+        <v>0.1572</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5849</v>
+        <v>0.1572</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5849</v>
+        <v>0.1572</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5849</v>
+        <v>0.1572</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5849</v>
+        <v>0.1572</v>
       </c>
       <c r="N30" t="n">
         <v>147</v>
@@ -1826,231 +1826,231 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>The eLiVe</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6659</v>
+        <v>-0.0939</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1233</v>
+        <v>-0.0174</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.6804</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6659</v>
+        <v>-0.0939</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0839</v>
+        <v>-0.0939</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.582</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0839</v>
+        <v>-0.0939</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.068</v>
+        <v>-0.0939</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.582</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="L31" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6499999999999999</v>
+        <v>-0.0939</v>
       </c>
       <c r="N31" t="n">
-        <v>209</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>beastik</t>
+          <t>MonttY</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6841</v>
+        <v>-0.2125</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1267</v>
+        <v>-0.0393</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7165</v>
+        <v>-0.7339</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6841</v>
+        <v>-0.2125</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6841</v>
+        <v>-0.2125</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6841</v>
+        <v>-0.2125</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6841</v>
+        <v>-0.2125</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6841</v>
+        <v>-0.2125</v>
       </c>
       <c r="N32" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MonttY</t>
+          <t>ponczek</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.722</v>
+        <v>-0.3079</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1337</v>
+        <v>-0.057</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7316</v>
+        <v>-0.777</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.722</v>
+        <v>-0.3079</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.722</v>
+        <v>-0.3079</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.722</v>
+        <v>-0.3079</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.722</v>
+        <v>-0.3079</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.722</v>
+        <v>-0.3079</v>
       </c>
       <c r="N33" t="n">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EYO</t>
+          <t>SOON</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9836</v>
+        <v>-0.4863</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1821</v>
+        <v>-0.09</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8358</v>
+        <v>-0.8576</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9836</v>
+        <v>-0.4863</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9836</v>
+        <v>-0.4863</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9836</v>
+        <v>-0.4863</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9836</v>
+        <v>-0.4863</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9836</v>
+        <v>-0.4863</v>
       </c>
       <c r="N34" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SOON</t>
+          <t>EYO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2058</v>
+        <v>-0.5854</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2233</v>
+        <v>-0.1084</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9243</v>
+        <v>-0.9023</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2058</v>
+        <v>-0.5854</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.2058</v>
+        <v>-0.5854</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.2058</v>
+        <v>-0.5854</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2058</v>
+        <v>-0.5854</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2058</v>
+        <v>-0.5854</v>
       </c>
       <c r="N35" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.522</v>
+        <v>-0.9344</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2818</v>
+        <v>-0.173</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0503</v>
+        <v>-1.0598</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.522</v>
+        <v>-0.9344</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.522</v>
+        <v>-0.9344</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.522</v>
+        <v>-0.9344</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.522</v>
+        <v>-0.9344</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.522</v>
+        <v>-0.9344</v>
       </c>
       <c r="N36" t="n">
         <v>147</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5321</v>
+        <v>-1.0229</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2837</v>
+        <v>-0.1894</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0543</v>
+        <v>-1.0998</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5321</v>
+        <v>-1.0229</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.5321</v>
+        <v>-1.0229</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.5321</v>
+        <v>-1.0229</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.5321</v>
+        <v>-1.0229</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.5321</v>
+        <v>-1.0229</v>
       </c>
       <c r="N37" t="n">
         <v>152</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>capseN</t>
+          <t>gabesson</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.8188</v>
+        <v>-1.2184</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3368</v>
+        <v>-0.2256</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1685</v>
+        <v>-1.1881</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.8188</v>
+        <v>-1.2184</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.8188</v>
+        <v>-1.2184</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.8188</v>
+        <v>-1.2184</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8188</v>
+        <v>-1.2184</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.8188</v>
+        <v>-1.2184</v>
       </c>
       <c r="N38" t="n">
         <v>147</v>
@@ -2194,32 +2194,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gabesson</t>
+          <t>capseN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8559</v>
+        <v>-1.2432</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3436</v>
+        <v>-0.2302</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1833</v>
+        <v>-1.1993</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8559</v>
+        <v>-1.2432</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8559</v>
+        <v>-1.2432</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8559</v>
+        <v>-1.2432</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8559</v>
+        <v>-1.2432</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8559</v>
+        <v>-1.2432</v>
       </c>
       <c r="N39" t="n">
         <v>147</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3236</v>
+        <v>-1.4352</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4302</v>
+        <v>-0.2657</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3696</v>
+        <v>-1.2859</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3236</v>
+        <v>-1.4352</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.3236</v>
+        <v>-1.4352</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.3236</v>
+        <v>-1.4352</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.3236</v>
+        <v>-1.4352</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3236</v>
+        <v>-1.4352</v>
       </c>
       <c r="N40" t="n">
         <v>152</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6137</v>
+        <v>-1.8035</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4839</v>
+        <v>-0.3339</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4852</v>
+        <v>-1.4522</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6137</v>
+        <v>-1.8035</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.6137</v>
+        <v>-1.8035</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.6137</v>
+        <v>-1.8035</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.6137</v>
+        <v>-1.8035</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.6137</v>
+        <v>-1.8035</v>
       </c>
       <c r="N41" t="n">
         <v>147</v>
@@ -2429,10 +2429,10 @@
         <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2226</v>
+        <v>0.2157</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3424</v>
+        <v>5.1768</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001</v>
+        <v>-0.0292</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.024</v>
+        <v>-0.7008</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0222</v>
+        <v>-0.0431</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-1.0344</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.63</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5762</v>
+        <v>-0.3812</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.8288</v>
+        <v>-9.1488</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.54</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6913</v>
+        <v>-0.4648</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.5912</v>
+        <v>-11.1552</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3756</v>
+        <v>1.2459</v>
       </c>
       <c r="J7" t="n">
-        <v>33.0144</v>
+        <v>29.9016</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8798</v>
+        <v>0.9056</v>
       </c>
       <c r="J8" t="n">
-        <v>21.1152</v>
+        <v>21.7344</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.27</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6411</v>
+        <v>0.7087</v>
       </c>
       <c r="J9" t="n">
-        <v>15.3864</v>
+        <v>17.0088</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>12.9072</v>
+        <v>14.7936</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.98</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2514</v>
+        <v>-0.1661</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.0336</v>
+        <v>-3.9864</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9292</v>
+        <v>0.8586</v>
       </c>
       <c r="J12" t="n">
-        <v>16.7256</v>
+        <v>15.4548</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.58</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7119</v>
+        <v>0.6622</v>
       </c>
       <c r="J13" t="n">
-        <v>12.8142</v>
+        <v>11.9196</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5392</v>
+        <v>0.5332</v>
       </c>
       <c r="J14" t="n">
-        <v>9.7056</v>
+        <v>9.5976</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.36</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4271</v>
+        <v>0.4376</v>
       </c>
       <c r="J15" t="n">
-        <v>7.6878</v>
+        <v>7.8768</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.32</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3772</v>
+        <v>0.3931</v>
       </c>
       <c r="J16" t="n">
-        <v>6.7896</v>
+        <v>7.0758</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2179</v>
+        <v>0.1619</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9222</v>
+        <v>2.9142</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3464</v>
+        <v>-0.2732</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.2352</v>
+        <v>-4.9176</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.57</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6039</v>
+        <v>-0.4108</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.8702</v>
+        <v>-7.3944</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.52</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.674</v>
+        <v>-0.4576</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.132</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.48</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7275</v>
+        <v>-0.4952</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.095</v>
+        <v>-8.913600000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.26</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4902</v>
+        <v>0.5732</v>
       </c>
       <c r="J22" t="n">
-        <v>14.706</v>
+        <v>17.196</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1145</v>
+        <v>-0.0825</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.435</v>
+        <v>-2.475</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.85</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2888</v>
+        <v>-0.1802</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.664</v>
+        <v>-5.406</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2888</v>
+        <v>-0.1802</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.664</v>
+        <v>-5.406</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.77</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4103</v>
+        <v>-0.2608</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.309</v>
+        <v>-7.824</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.069</v>
+        <v>1.0346</v>
       </c>
       <c r="J27" t="n">
-        <v>32.07</v>
+        <v>31.038</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.069</v>
+        <v>1.0346</v>
       </c>
       <c r="J28" t="n">
-        <v>32.07</v>
+        <v>31.038</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3835</v>
+        <v>-0.3176</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.505</v>
+        <v>-9.528</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4416</v>
+        <v>-0.3767</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.248</v>
+        <v>-11.301</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5242</v>
+        <v>-0.4618</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.726</v>
+        <v>-13.854</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.42</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1047</v>
+        <v>0.7864</v>
       </c>
       <c r="J32" t="n">
-        <v>33.141</v>
+        <v>23.592</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4351</v>
+        <v>0.3889</v>
       </c>
       <c r="J33" t="n">
-        <v>13.053</v>
+        <v>11.667</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1415</v>
       </c>
       <c r="J34" t="n">
-        <v>2.814</v>
+        <v>4.245</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.99</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1444</v>
+        <v>-0.0803</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.332</v>
+        <v>-2.409</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2611</v>
+        <v>-0.1935</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.833</v>
+        <v>-5.805</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.39</v>
       </c>
       <c r="I37" t="n">
-        <v>0.627</v>
+        <v>0.5865</v>
       </c>
       <c r="J37" t="n">
-        <v>18.81</v>
+        <v>17.595</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.98</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0377</v>
       </c>
       <c r="J38" t="n">
-        <v>-2.331</v>
+        <v>-1.131</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.101</v>
+        <v>-0.0519</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.03</v>
+        <v>-1.557</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.91</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2169</v>
+        <v>-0.1252</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.507</v>
+        <v>-3.756</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3142</v>
+        <v>-0.1902</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.426</v>
+        <v>-5.706</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0995</v>
+        <v>0.7943</v>
       </c>
       <c r="J42" t="n">
-        <v>31.8855</v>
+        <v>23.0347</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9502</v>
+        <v>0.7039</v>
       </c>
       <c r="J43" t="n">
-        <v>27.5558</v>
+        <v>20.4131</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7664</v>
+        <v>0.5985</v>
       </c>
       <c r="J44" t="n">
-        <v>22.2256</v>
+        <v>17.3565</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.27</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6911</v>
+        <v>0.5585</v>
       </c>
       <c r="J45" t="n">
-        <v>20.0419</v>
+        <v>16.1965</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7161</v>
+        <v>-0.659</v>
       </c>
       <c r="J46" t="n">
-        <v>-20.7669</v>
+        <v>-19.111</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4256</v>
+        <v>0.4237</v>
       </c>
       <c r="J47" t="n">
-        <v>12.3424</v>
+        <v>12.2873</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2576</v>
+        <v>0.2694</v>
       </c>
       <c r="J48" t="n">
-        <v>7.4704</v>
+        <v>7.8126</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.86</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2678</v>
+        <v>-0.1685</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.7662</v>
+        <v>-4.8865</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.76</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4214</v>
+        <v>-0.2691</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.2206</v>
+        <v>-7.8039</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5311</v>
+        <v>-0.346</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.4019</v>
+        <v>-10.034</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5271</v>
+        <v>0.5113</v>
       </c>
       <c r="J52" t="n">
-        <v>15.813</v>
+        <v>15.339</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.118</v>
+        <v>0.1686</v>
       </c>
       <c r="J53" t="n">
-        <v>3.54</v>
+        <v>5.058</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.118</v>
+        <v>0.1686</v>
       </c>
       <c r="J54" t="n">
-        <v>3.54</v>
+        <v>5.058</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.118</v>
+        <v>0.1686</v>
       </c>
       <c r="J55" t="n">
-        <v>3.54</v>
+        <v>5.058</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.95</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1664</v>
+        <v>-0.0861</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.992</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8662</v>
+        <v>0.629</v>
       </c>
       <c r="J57" t="n">
-        <v>25.986</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.11</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4071</v>
+        <v>0.354</v>
       </c>
       <c r="J58" t="n">
-        <v>12.213</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3198</v>
+        <v>-0.2677</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.593999999999999</v>
+        <v>-8.031000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.91</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3815</v>
+        <v>-0.3277</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.445</v>
+        <v>-9.831</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4111</v>
+        <v>-0.3569</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.333</v>
+        <v>-10.707</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.28</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5127</v>
+        <v>0.4931</v>
       </c>
       <c r="J62" t="n">
-        <v>13.3302</v>
+        <v>12.8206</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2485</v>
+        <v>0.2615</v>
       </c>
       <c r="J63" t="n">
-        <v>6.461</v>
+        <v>6.799</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.85</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2929</v>
+        <v>-0.1816</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.6154</v>
+        <v>-4.7216</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3549</v>
+        <v>-0.2225</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.227399999999999</v>
+        <v>-5.785</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5229</v>
+        <v>-0.3394</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.5954</v>
+        <v>-8.824400000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0457</v>
+        <v>0.7593</v>
       </c>
       <c r="J67" t="n">
-        <v>27.1882</v>
+        <v>19.7418</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.3</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7776</v>
+        <v>0.601</v>
       </c>
       <c r="J68" t="n">
-        <v>20.2176</v>
+        <v>15.626</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5004</v>
+        <v>0.4653</v>
       </c>
       <c r="J69" t="n">
-        <v>13.0104</v>
+        <v>12.0978</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.14</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3366</v>
+        <v>0.3764</v>
       </c>
       <c r="J70" t="n">
-        <v>8.7516</v>
+        <v>9.7864</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1056</v>
+        <v>0.1783</v>
       </c>
       <c r="J71" t="n">
-        <v>2.7456</v>
+        <v>4.6358</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6758</v>
+        <v>1.4441</v>
       </c>
       <c r="J72" t="n">
-        <v>40.2192</v>
+        <v>34.6584</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.55</v>
       </c>
       <c r="I73" t="n">
-        <v>1.2657</v>
+        <v>1.1788</v>
       </c>
       <c r="J73" t="n">
-        <v>30.3768</v>
+        <v>28.2912</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.34</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8137</v>
+        <v>0.8568</v>
       </c>
       <c r="J74" t="n">
-        <v>19.5288</v>
+        <v>20.5632</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.042</v>
+        <v>0.1246</v>
       </c>
       <c r="J75" t="n">
-        <v>1.008</v>
+        <v>2.9904</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.87</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.5152</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.0448</v>
+        <v>-12.3648</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.18</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3846</v>
+        <v>0.4317</v>
       </c>
       <c r="J77" t="n">
-        <v>9.230399999999999</v>
+        <v>10.3608</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3698</v>
+        <v>0.4123</v>
       </c>
       <c r="J78" t="n">
-        <v>8.8752</v>
+        <v>9.895200000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.77</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4054</v>
+        <v>-0.2586</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.7296</v>
+        <v>-6.2064</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4198</v>
+        <v>-0.2684</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.0752</v>
+        <v>-6.4416</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5031</v>
+        <v>-0.3262</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.0744</v>
+        <v>-7.8288</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0862</v>
+        <v>0.0847</v>
       </c>
       <c r="J82" t="n">
-        <v>1.5516</v>
+        <v>1.5246</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.54</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.5173</v>
+        <v>-0.4063</v>
       </c>
       <c r="J83" t="n">
-        <v>-9.311400000000001</v>
+        <v>-7.3134</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.47</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.6571</v>
+        <v>-0.4699</v>
       </c>
       <c r="J84" t="n">
-        <v>-11.8278</v>
+        <v>-8.4582</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.25</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.9798</v>
+        <v>-0.6863</v>
       </c>
       <c r="J85" t="n">
-        <v>-17.6364</v>
+        <v>-12.3534</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.25</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.9798</v>
+        <v>-0.6863</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.6364</v>
+        <v>-12.3534</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>2.07</v>
       </c>
       <c r="I87" t="n">
-        <v>1.9898</v>
+        <v>1.7036</v>
       </c>
       <c r="J87" t="n">
-        <v>35.8164</v>
+        <v>30.6648</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.9</v>
       </c>
       <c r="I88" t="n">
-        <v>1.7554</v>
+        <v>1.5213</v>
       </c>
       <c r="J88" t="n">
-        <v>31.5972</v>
+        <v>27.3834</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.74</v>
       </c>
       <c r="I89" t="n">
-        <v>1.4637</v>
+        <v>1.3476</v>
       </c>
       <c r="J89" t="n">
-        <v>26.3466</v>
+        <v>24.2568</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.52</v>
       </c>
       <c r="I90" t="n">
-        <v>1.006</v>
+        <v>1.1012</v>
       </c>
       <c r="J90" t="n">
-        <v>18.108</v>
+        <v>19.8216</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.18</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2988</v>
+        <v>0.415</v>
       </c>
       <c r="J91" t="n">
-        <v>5.3784</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.38</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9427</v>
+        <v>0.9544</v>
       </c>
       <c r="J92" t="n">
-        <v>24.5102</v>
+        <v>24.8144</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.27</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6795</v>
+        <v>0.7126</v>
       </c>
       <c r="J93" t="n">
-        <v>17.667</v>
+        <v>18.5276</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.23</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5584</v>
+        <v>0.6223</v>
       </c>
       <c r="J94" t="n">
-        <v>14.5184</v>
+        <v>16.1798</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.21</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5053</v>
+        <v>0.5749</v>
       </c>
       <c r="J95" t="n">
-        <v>13.1378</v>
+        <v>14.9474</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.19</v>
       </c>
       <c r="I96" t="n">
-        <v>0.453</v>
+        <v>0.5262</v>
       </c>
       <c r="J96" t="n">
-        <v>11.778</v>
+        <v>13.6812</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.09</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2832</v>
+        <v>0.2928</v>
       </c>
       <c r="J97" t="n">
-        <v>7.3632</v>
+        <v>7.6128</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1455</v>
+        <v>-0.125</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.783</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2968</v>
+        <v>-0.2072</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.7168</v>
+        <v>-5.3872</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.71</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4601</v>
+        <v>-0.303</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.9626</v>
+        <v>-7.878</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6499</v>
+        <v>-0.4346</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.8974</v>
+        <v>-11.2996</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6922</v>
       </c>
       <c r="J102" t="n">
-        <v>19.7428</v>
+        <v>19.3816</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.18</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5235</v>
+        <v>0.5214</v>
       </c>
       <c r="J103" t="n">
-        <v>14.658</v>
+        <v>14.5992</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4336</v>
+        <v>0.4464</v>
       </c>
       <c r="J104" t="n">
-        <v>12.1408</v>
+        <v>12.4992</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2682</v>
+        <v>0.3152</v>
       </c>
       <c r="J105" t="n">
-        <v>7.5096</v>
+        <v>8.8256</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.04</v>
       </c>
       <c r="I106" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1332</v>
       </c>
       <c r="J106" t="n">
-        <v>2.1084</v>
+        <v>3.7296</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.07</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2092</v>
+        <v>0.2079</v>
       </c>
       <c r="J107" t="n">
-        <v>5.8576</v>
+        <v>5.8212</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.99</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0128</v>
+        <v>-0.0118</v>
       </c>
       <c r="J108" t="n">
-        <v>0.3584</v>
+        <v>-0.3304</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2637</v>
+        <v>-0.1673</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.3836</v>
+        <v>-4.6844</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3131</v>
+        <v>-0.1982</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.7668</v>
+        <v>-5.5496</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3444</v>
+        <v>-0.2184</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.6432</v>
+        <v>-6.1152</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1853</v>
+        <v>0.1809</v>
       </c>
       <c r="J112" t="n">
-        <v>4.8178</v>
+        <v>4.7034</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0418</v>
+        <v>0.0138</v>
       </c>
       <c r="J113" t="n">
-        <v>1.0868</v>
+        <v>0.3588</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0698</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.262</v>
+        <v>-1.8148</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1789</v>
+        <v>-0.1155</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.6514</v>
+        <v>-3.003</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.71</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4919</v>
+        <v>-0.3179</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.7894</v>
+        <v>-8.2654</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9654</v>
+        <v>0.9584</v>
       </c>
       <c r="J117" t="n">
-        <v>25.1004</v>
+        <v>24.9184</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6879</v>
+        <v>0.6843</v>
       </c>
       <c r="J118" t="n">
-        <v>17.8854</v>
+        <v>17.7918</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6127</v>
       </c>
       <c r="J119" t="n">
-        <v>15.8964</v>
+        <v>15.9302</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>0.16</v>
+        <v>0.2217</v>
       </c>
       <c r="J120" t="n">
-        <v>4.16</v>
+        <v>5.7642</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3189</v>
+        <v>-0.2433</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.291399999999999</v>
+        <v>-6.3258</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4261</v>
+        <v>0.4933</v>
       </c>
       <c r="J122" t="n">
-        <v>12.783</v>
+        <v>14.799</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3979</v>
+        <v>0.457</v>
       </c>
       <c r="J123" t="n">
-        <v>11.937</v>
+        <v>13.71</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.04</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1145</v>
+        <v>0.1161</v>
       </c>
       <c r="J124" t="n">
-        <v>3.435</v>
+        <v>3.483</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1927</v>
+        <v>-0.1117</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.781</v>
+        <v>-3.351</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6458</v>
+        <v>-0.4292</v>
       </c>
       <c r="J126" t="n">
-        <v>-19.374</v>
+        <v>-12.876</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.63</v>
       </c>
       <c r="I127" t="n">
-        <v>1.528</v>
+        <v>1.3409</v>
       </c>
       <c r="J127" t="n">
-        <v>45.84</v>
+        <v>40.227</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1742</v>
+        <v>0.2093</v>
       </c>
       <c r="J128" t="n">
-        <v>5.226</v>
+        <v>6.279</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1795</v>
+        <v>-0.1171</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.385</v>
+        <v>-3.513</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3202</v>
+        <v>-0.2548</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.606</v>
+        <v>-7.644</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5493</v>
+        <v>-0.4883</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.479</v>
+        <v>-14.649</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0244</v>
+        <v>1.0049</v>
       </c>
       <c r="J132" t="n">
-        <v>26.6344</v>
+        <v>26.1274</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7305</v>
+        <v>0.7168</v>
       </c>
       <c r="J133" t="n">
-        <v>18.993</v>
+        <v>18.6368</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3629</v>
+        <v>0.3963</v>
       </c>
       <c r="J134" t="n">
-        <v>9.4354</v>
+        <v>10.3038</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.1337</v>
       </c>
       <c r="J135" t="n">
-        <v>1.9838</v>
+        <v>3.4762</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4854</v>
+        <v>-0.4173</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.6204</v>
+        <v>-10.8498</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2933</v>
+        <v>0.3095</v>
       </c>
       <c r="J137" t="n">
-        <v>7.6258</v>
+        <v>8.047000000000001</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2066</v>
+        <v>0.1994</v>
       </c>
       <c r="J138" t="n">
-        <v>5.3716</v>
+        <v>5.1844</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.83</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2966</v>
+        <v>-0.1935</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.7116</v>
+        <v>-5.031</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3766</v>
+        <v>-0.2431</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.791600000000001</v>
+        <v>-6.3206</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6492</v>
+        <v>-0.433</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.8792</v>
+        <v>-11.258</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2917</v>
+        <v>1.185</v>
       </c>
       <c r="J142" t="n">
-        <v>34.8759</v>
+        <v>31.995</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.39</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0045</v>
+        <v>0.9936</v>
       </c>
       <c r="J143" t="n">
-        <v>27.1215</v>
+        <v>26.8272</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3626</v>
+        <v>0.4153</v>
       </c>
       <c r="J144" t="n">
-        <v>9.7902</v>
+        <v>11.2131</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0147</v>
+        <v>0.0524</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.3969</v>
+        <v>1.4148</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6768</v>
+        <v>-0.6182</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.2736</v>
+        <v>-16.6914</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4921</v>
+        <v>0.5746</v>
       </c>
       <c r="J147" t="n">
-        <v>13.2867</v>
+        <v>15.5142</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1388</v>
+        <v>0.119</v>
       </c>
       <c r="J148" t="n">
-        <v>3.7476</v>
+        <v>3.213</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3374</v>
+        <v>-0.2159</v>
       </c>
       <c r="J149" t="n">
-        <v>-9.1098</v>
+        <v>-5.8293</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.353</v>
+        <v>-0.2259</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.531000000000001</v>
+        <v>-6.0993</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6653</v>
+        <v>-0.4447</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.9631</v>
+        <v>-12.0069</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0885</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.523</v>
+        <v>-2.5665</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1931</v>
+        <v>-0.1561</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.5999</v>
+        <v>-4.5269</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.86</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1931</v>
+        <v>-0.1561</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.5999</v>
+        <v>-4.5269</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2458</v>
+        <v>-0.187</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.1282</v>
+        <v>-5.423</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6731</v>
+        <v>-0.4518</v>
       </c>
       <c r="J156" t="n">
-        <v>-19.5199</v>
+        <v>-13.1022</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.67</v>
       </c>
       <c r="I157" t="n">
-        <v>1.508</v>
+        <v>1.3318</v>
       </c>
       <c r="J157" t="n">
-        <v>43.732</v>
+        <v>38.6222</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I158" t="n">
-        <v>1.16</v>
+        <v>1.1102</v>
       </c>
       <c r="J158" t="n">
-        <v>33.64</v>
+        <v>32.1958</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.39</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9485</v>
+        <v>0.9665</v>
       </c>
       <c r="J159" t="n">
-        <v>27.5065</v>
+        <v>28.0285</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0829</v>
+        <v>0.1634</v>
       </c>
       <c r="J160" t="n">
-        <v>2.4041</v>
+        <v>4.7386</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.82</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7019</v>
+        <v>-0.6427</v>
       </c>
       <c r="J161" t="n">
-        <v>-20.3551</v>
+        <v>-18.6383</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.73</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5247</v>
+        <v>1.359</v>
       </c>
       <c r="J162" t="n">
-        <v>32.0187</v>
+        <v>28.539</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.64</v>
       </c>
       <c r="I163" t="n">
-        <v>1.3556</v>
+        <v>1.2557</v>
       </c>
       <c r="J163" t="n">
-        <v>28.4676</v>
+        <v>26.3697</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.61</v>
       </c>
       <c r="I164" t="n">
-        <v>1.2969</v>
+        <v>1.221</v>
       </c>
       <c r="J164" t="n">
-        <v>27.2349</v>
+        <v>25.641</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.58</v>
       </c>
       <c r="I165" t="n">
-        <v>1.2366</v>
+        <v>1.1863</v>
       </c>
       <c r="J165" t="n">
-        <v>25.9686</v>
+        <v>24.9123</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.95</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4015</v>
+        <v>-0.316</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.4315</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.83</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1613</v>
+        <v>-0.1518</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.3873</v>
+        <v>-3.1878</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.74</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3031</v>
+        <v>-0.2487</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.3651</v>
+        <v>-5.2227</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.67</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.416</v>
+        <v>-0.3173</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.736000000000001</v>
+        <v>-6.6633</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.52</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6669</v>
+        <v>-0.454</v>
       </c>
       <c r="J170" t="n">
-        <v>-14.0049</v>
+        <v>-9.534000000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.45</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7611</v>
+        <v>-0.52</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.9831</v>
+        <v>-10.92</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.85</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1097</v>
+        <v>-0.1156</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.8649</v>
+        <v>-1.9652</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.78</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2207</v>
+        <v>-0.1958</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.7519</v>
+        <v>-3.3286</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.54</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.6224</v>
+        <v>-0.4287</v>
       </c>
       <c r="J174" t="n">
-        <v>-10.5808</v>
+        <v>-7.2879</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6666</v>
+        <v>-0.4567</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.3322</v>
+        <v>-7.7639</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.35</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.88</v>
+        <v>-0.6089</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.96</v>
+        <v>-10.3513</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.83</v>
       </c>
       <c r="I177" t="n">
-        <v>1.7052</v>
+        <v>1.4733</v>
       </c>
       <c r="J177" t="n">
-        <v>28.9884</v>
+        <v>25.0461</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.67</v>
       </c>
       <c r="I178" t="n">
-        <v>1.4148</v>
+        <v>1.2908</v>
       </c>
       <c r="J178" t="n">
-        <v>24.0516</v>
+        <v>21.9436</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.46</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9604</v>
+        <v>1.0468</v>
       </c>
       <c r="J179" t="n">
-        <v>16.3268</v>
+        <v>17.7956</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.45</v>
       </c>
       <c r="I180" t="n">
-        <v>0.9381</v>
+        <v>1.0337</v>
       </c>
       <c r="J180" t="n">
-        <v>15.9477</v>
+        <v>17.5729</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.08</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0839</v>
+        <v>0.1784</v>
       </c>
       <c r="J181" t="n">
-        <v>1.4263</v>
+        <v>3.0328</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.46</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7531</v>
+        <v>0.9406</v>
       </c>
       <c r="J182" t="n">
-        <v>21.8399</v>
+        <v>27.2774</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2317</v>
+        <v>0.2342</v>
       </c>
       <c r="J183" t="n">
-        <v>6.7193</v>
+        <v>6.7918</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.74</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4439</v>
+        <v>-0.2858</v>
       </c>
       <c r="J184" t="n">
-        <v>-12.8731</v>
+        <v>-8.2882</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4993</v>
+        <v>-0.3242</v>
       </c>
       <c r="J185" t="n">
-        <v>-14.4797</v>
+        <v>-9.4018</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.4913</v>
       </c>
       <c r="J186" t="n">
-        <v>-21.0917</v>
+        <v>-14.2477</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.48</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1543</v>
+        <v>1.1035</v>
       </c>
       <c r="J187" t="n">
-        <v>33.4747</v>
+        <v>32.0015</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.47</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1338</v>
+        <v>1.0908</v>
       </c>
       <c r="J188" t="n">
-        <v>32.8802</v>
+        <v>31.6332</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.35</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8754</v>
+        <v>0.8915</v>
       </c>
       <c r="J189" t="n">
-        <v>25.3866</v>
+        <v>25.8535</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.35</v>
       </c>
       <c r="I190" t="n">
-        <v>0.8754</v>
+        <v>0.8915</v>
       </c>
       <c r="J190" t="n">
-        <v>25.3866</v>
+        <v>25.8535</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.1121</v>
+        <v>-1.1024</v>
       </c>
       <c r="J191" t="n">
-        <v>-32.2509</v>
+        <v>-31.9696</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.3</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5475</v>
+        <v>0.6509</v>
       </c>
       <c r="J192" t="n">
-        <v>14.235</v>
+        <v>16.9234</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3221</v>
+        <v>0.3511</v>
       </c>
       <c r="J193" t="n">
-        <v>8.374599999999999</v>
+        <v>9.1286</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.08</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2232</v>
+        <v>0.2267</v>
       </c>
       <c r="J194" t="n">
-        <v>5.8032</v>
+        <v>5.8942</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5572</v>
+        <v>-0.3648</v>
       </c>
       <c r="J195" t="n">
-        <v>-14.4872</v>
+        <v>-9.4848</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.43</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8349</v>
+        <v>-0.5745</v>
       </c>
       <c r="J196" t="n">
-        <v>-21.7074</v>
+        <v>-14.937</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.95</v>
       </c>
       <c r="I197" t="n">
-        <v>1.9676</v>
+        <v>1.6666</v>
       </c>
       <c r="J197" t="n">
-        <v>51.1576</v>
+        <v>43.3316</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.4</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9737</v>
+        <v>0.9859</v>
       </c>
       <c r="J198" t="n">
-        <v>25.3162</v>
+        <v>25.6334</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.14</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3107</v>
+        <v>0.3932</v>
       </c>
       <c r="J199" t="n">
-        <v>8.078200000000001</v>
+        <v>10.2232</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.15</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.9</v>
+        <v>-1.7706</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4704</v>
+        <v>-0.3934</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.2304</v>
+        <v>-10.2284</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.59</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3574</v>
+        <v>1.2342</v>
       </c>
       <c r="J202" t="n">
-        <v>28.5054</v>
+        <v>25.9182</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9263</v>
+        <v>0.9473</v>
       </c>
       <c r="J203" t="n">
-        <v>19.4523</v>
+        <v>19.8933</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.27</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6428</v>
+        <v>0.709</v>
       </c>
       <c r="J204" t="n">
-        <v>13.4988</v>
+        <v>14.889</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.2</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4629</v>
+        <v>0.5445</v>
       </c>
       <c r="J205" t="n">
-        <v>9.7209</v>
+        <v>11.4345</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.99</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2096</v>
+        <v>-0.1245</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.4016</v>
+        <v>-2.6145</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.01</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1583</v>
+        <v>0.1309</v>
       </c>
       <c r="J207" t="n">
-        <v>3.3243</v>
+        <v>2.7489</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1916</v>
+        <v>-0.1649</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.0236</v>
+        <v>-3.4629</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.76</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3245</v>
+        <v>-0.2464</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.8145</v>
+        <v>-5.1744</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.74</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3615</v>
+        <v>-0.265</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.5915</v>
+        <v>-5.565</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.32</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.9378</v>
+        <v>-0.6546</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.6938</v>
+        <v>-13.7466</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.48</v>
       </c>
       <c r="I212" t="n">
-        <v>0.742</v>
+        <v>0.9216</v>
       </c>
       <c r="J212" t="n">
-        <v>20.776</v>
+        <v>25.8048</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.176</v>
+        <v>0.1845</v>
       </c>
       <c r="J213" t="n">
-        <v>4.928</v>
+        <v>5.166</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0925</v>
       </c>
       <c r="J214" t="n">
-        <v>2.6404</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.84</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3233</v>
+        <v>-0.1979</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.0524</v>
+        <v>-5.5412</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6933</v>
+        <v>-0.4652</v>
       </c>
       <c r="J216" t="n">
-        <v>-19.4124</v>
+        <v>-13.0256</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.36</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9432</v>
       </c>
       <c r="J217" t="n">
-        <v>26.6588</v>
+        <v>26.4096</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.29</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7937</v>
+        <v>0.7834</v>
       </c>
       <c r="J218" t="n">
-        <v>22.2236</v>
+        <v>21.9352</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.11</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2905</v>
+        <v>0.3403</v>
       </c>
       <c r="J219" t="n">
-        <v>8.134</v>
+        <v>9.5284</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.1</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2604</v>
+        <v>0.3126</v>
       </c>
       <c r="J220" t="n">
-        <v>7.2912</v>
+        <v>8.752800000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.92</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4053</v>
+        <v>-0.3331</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.3484</v>
+        <v>-9.3268</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.93</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.0387</v>
+        <v>-0.0611</v>
       </c>
       <c r="J222" t="n">
-        <v>-0.8127</v>
+        <v>-1.2831</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.76</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.3273</v>
+        <v>-0.2469</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.8733</v>
+        <v>-5.1849</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.71</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.426</v>
+        <v>-0.2925</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.946</v>
+        <v>-6.1425</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.7</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4425</v>
+        <v>-0.3018</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.2925</v>
+        <v>-6.3378</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.59</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6035</v>
+        <v>-0.4047</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.6735</v>
+        <v>-8.498699999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.92</v>
       </c>
       <c r="I227" t="n">
-        <v>1.8675</v>
+        <v>1.58</v>
       </c>
       <c r="J227" t="n">
-        <v>39.2175</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2112</v>
+        <v>1.1664</v>
       </c>
       <c r="J228" t="n">
-        <v>25.4352</v>
+        <v>24.4944</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.42</v>
       </c>
       <c r="I229" t="n">
-        <v>0.8855</v>
+        <v>0.9919</v>
       </c>
       <c r="J229" t="n">
-        <v>18.5955</v>
+        <v>20.8299</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.36</v>
       </c>
       <c r="I230" t="n">
-        <v>0.7534</v>
+        <v>0.875</v>
       </c>
       <c r="J230" t="n">
-        <v>15.8214</v>
+        <v>18.375</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.1</v>
       </c>
       <c r="I231" t="n">
-        <v>0.1447</v>
+        <v>0.2416</v>
       </c>
       <c r="J231" t="n">
-        <v>3.0387</v>
+        <v>5.0736</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.46</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7147</v>
+        <v>0.8838</v>
       </c>
       <c r="J232" t="n">
-        <v>21.441</v>
+        <v>26.514</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1583</v>
+        <v>-0.089</v>
       </c>
       <c r="J233" t="n">
-        <v>-4.749</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1954</v>
+        <v>-0.1125</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.862</v>
+        <v>-3.375</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.87</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2798</v>
+        <v>-0.1678</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.394</v>
+        <v>-5.034</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3111</v>
+        <v>-0.1889</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.333</v>
+        <v>-5.667</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.32</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8914</v>
+        <v>0.8729</v>
       </c>
       <c r="J237" t="n">
-        <v>26.742</v>
+        <v>26.187</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.29</v>
       </c>
       <c r="I238" t="n">
-        <v>0.823</v>
+        <v>0.8017</v>
       </c>
       <c r="J238" t="n">
-        <v>24.69</v>
+        <v>24.051</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.1</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3033</v>
+        <v>0.3227</v>
       </c>
       <c r="J239" t="n">
-        <v>9.099</v>
+        <v>9.680999999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3245</v>
+        <v>-0.2575</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.734999999999999</v>
+        <v>-7.725</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.87</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5264</v>
+        <v>-0.4634</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.792</v>
+        <v>-13.902</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3083</v>
+        <v>0.3254</v>
       </c>
       <c r="J242" t="n">
-        <v>7.0909</v>
+        <v>7.4842</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.86</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1879</v>
+        <v>-0.1545</v>
       </c>
       <c r="J243" t="n">
-        <v>-4.3217</v>
+        <v>-3.5535</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.74</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4068</v>
+        <v>-0.2716</v>
       </c>
       <c r="J244" t="n">
-        <v>-9.356400000000001</v>
+        <v>-6.2468</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.66</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.3475</v>
       </c>
       <c r="J245" t="n">
-        <v>-12.0681</v>
+        <v>-7.9925</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.61</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5929</v>
+        <v>-0.3945</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.6367</v>
+        <v>-9.073499999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.63</v>
       </c>
       <c r="I247" t="n">
-        <v>1.408</v>
+        <v>1.2709</v>
       </c>
       <c r="J247" t="n">
-        <v>32.384</v>
+        <v>29.2307</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.56</v>
       </c>
       <c r="I248" t="n">
-        <v>1.2733</v>
+        <v>1.1861</v>
       </c>
       <c r="J248" t="n">
-        <v>29.2859</v>
+        <v>27.2803</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.31</v>
       </c>
       <c r="I249" t="n">
-        <v>0.7047</v>
+        <v>0.789</v>
       </c>
       <c r="J249" t="n">
-        <v>16.2081</v>
+        <v>18.147</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.15</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3129</v>
+        <v>0.4056</v>
       </c>
       <c r="J250" t="n">
-        <v>7.1967</v>
+        <v>9.328799999999999</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.06</v>
       </c>
       <c r="I251" t="n">
-        <v>0.0653</v>
+        <v>0.1505</v>
       </c>
       <c r="J251" t="n">
-        <v>1.5019</v>
+        <v>3.4615</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.11</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2772</v>
+        <v>0.2931</v>
       </c>
       <c r="J252" t="n">
-        <v>7.2072</v>
+        <v>7.6206</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.08</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2263</v>
+        <v>0.2293</v>
       </c>
       <c r="J253" t="n">
-        <v>5.8838</v>
+        <v>5.9618</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.86</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2645</v>
+        <v>-0.1676</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.877</v>
+        <v>-4.3576</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.78</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3902</v>
+        <v>-0.2485</v>
       </c>
       <c r="J255" t="n">
-        <v>-10.1452</v>
+        <v>-6.461</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.74</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4476</v>
+        <v>-0.2876</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.6376</v>
+        <v>-7.4776</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.51</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2255</v>
+        <v>1.1462</v>
       </c>
       <c r="J257" t="n">
-        <v>31.863</v>
+        <v>29.8012</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0194</v>
+        <v>1.0131</v>
       </c>
       <c r="J258" t="n">
-        <v>26.5044</v>
+        <v>26.3406</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.14</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3316</v>
+        <v>0.4036</v>
       </c>
       <c r="J259" t="n">
-        <v>8.621600000000001</v>
+        <v>10.4936</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1918</v>
+        <v>0.2659</v>
       </c>
       <c r="J260" t="n">
-        <v>4.9868</v>
+        <v>6.9134</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.02</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.0353</v>
+        <v>0.0389</v>
       </c>
       <c r="J261" t="n">
-        <v>-0.9177999999999999</v>
+        <v>1.0114</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.69</v>
       </c>
       <c r="I262" t="n">
-        <v>1.6266</v>
+        <v>1.4084</v>
       </c>
       <c r="J262" t="n">
-        <v>35.7852</v>
+        <v>30.9848</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.29</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8152</v>
+        <v>0.7964</v>
       </c>
       <c r="J263" t="n">
-        <v>17.9344</v>
+        <v>17.5208</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3303</v>
+        <v>-0.2613</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.2666</v>
+        <v>-5.7486</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.85</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5836</v>
+        <v>-0.5221</v>
       </c>
       <c r="J265" t="n">
-        <v>-12.8392</v>
+        <v>-11.4862</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.82</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6592</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.5024</v>
+        <v>-13.2506</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.21</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4293</v>
+        <v>0.4905</v>
       </c>
       <c r="J267" t="n">
-        <v>9.444599999999999</v>
+        <v>10.791</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.87</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2464</v>
+        <v>-0.1569</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.4208</v>
+        <v>-3.4518</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.297</v>
+        <v>-0.188</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.534</v>
+        <v>-4.136</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.82</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3289</v>
+        <v>-0.2083</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.2358</v>
+        <v>-4.5826</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.82</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3289</v>
+        <v>-0.2083</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.2358</v>
+        <v>-4.5826</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.442</v>
+        <v>0.5134</v>
       </c>
       <c r="J272" t="n">
-        <v>13.26</v>
+        <v>15.402</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.13</v>
       </c>
       <c r="I273" t="n">
-        <v>0.2798</v>
+        <v>0.3079</v>
       </c>
       <c r="J273" t="n">
-        <v>8.394</v>
+        <v>9.237</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.04</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1173</v>
+        <v>0.1172</v>
       </c>
       <c r="J274" t="n">
-        <v>3.519</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.85</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3074</v>
+        <v>-0.1873</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.222</v>
+        <v>-5.619</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.506</v>
+        <v>-0.3261</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.18</v>
+        <v>-9.782999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.29</v>
       </c>
       <c r="I277" t="n">
-        <v>0.475</v>
+        <v>0.5679</v>
       </c>
       <c r="J277" t="n">
-        <v>14.25</v>
+        <v>17.037</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.18</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3193</v>
+        <v>0.3766</v>
       </c>
       <c r="J278" t="n">
-        <v>9.579000000000001</v>
+        <v>11.298</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2208</v>
+        <v>0.2662</v>
       </c>
       <c r="J279" t="n">
-        <v>6.624</v>
+        <v>7.986</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.0368</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="J280" t="n">
-        <v>1.104</v>
+        <v>2.331</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.87</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3013</v>
+        <v>-0.1777</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.039</v>
+        <v>-5.331</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.12</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3245</v>
+        <v>0.3478</v>
       </c>
       <c r="J282" t="n">
-        <v>8.112500000000001</v>
+        <v>8.695</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.11</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3083</v>
+        <v>0.3266</v>
       </c>
       <c r="J283" t="n">
-        <v>7.7075</v>
+        <v>8.164999999999999</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.77</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3773</v>
+        <v>-0.248</v>
       </c>
       <c r="J284" t="n">
-        <v>-9.432499999999999</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.6</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.6159</v>
+        <v>-0.4095</v>
       </c>
       <c r="J285" t="n">
-        <v>-15.3975</v>
+        <v>-10.2375</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.57</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6542</v>
+        <v>-0.4373</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.355</v>
+        <v>-10.9325</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.59</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3435</v>
+        <v>1.2278</v>
       </c>
       <c r="J287" t="n">
-        <v>33.5875</v>
+        <v>30.695</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.33</v>
       </c>
       <c r="I288" t="n">
-        <v>0.7879</v>
+        <v>0.8353</v>
       </c>
       <c r="J288" t="n">
-        <v>19.6975</v>
+        <v>20.8825</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.31</v>
       </c>
       <c r="I289" t="n">
-        <v>0.7258</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="J289" t="n">
-        <v>18.145</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.31</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7258</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="J290" t="n">
-        <v>18.145</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I291" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0914</v>
       </c>
       <c r="J291" t="n">
-        <v>0.24</v>
+        <v>2.285</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1513</v>
+        <v>1.1068</v>
       </c>
       <c r="J292" t="n">
-        <v>28.7825</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.34</v>
       </c>
       <c r="I293" t="n">
-        <v>0.8224</v>
+        <v>0.8589</v>
       </c>
       <c r="J293" t="n">
-        <v>20.56</v>
+        <v>21.4725</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.31</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7444</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="J294" t="n">
-        <v>18.61</v>
+        <v>19.8475</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.26</v>
       </c>
       <c r="I295" t="n">
-        <v>0.604</v>
+        <v>0.6832</v>
       </c>
       <c r="J295" t="n">
-        <v>15.1</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.12</v>
       </c>
       <c r="I296" t="n">
-        <v>0.248</v>
+        <v>0.3339</v>
       </c>
       <c r="J296" t="n">
-        <v>6.2</v>
+        <v>8.3475</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.07</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2385</v>
+        <v>0.2364</v>
       </c>
       <c r="J297" t="n">
-        <v>5.9625</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1026</v>
+        <v>-0.0945</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.565</v>
+        <v>-2.3625</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3306</v>
+        <v>-0.2193</v>
       </c>
       <c r="J299" t="n">
-        <v>-8.265000000000001</v>
+        <v>-5.4825</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.72</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4538</v>
+        <v>-0.2968</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.345</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5102</v>
+        <v>-0.3349</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.755</v>
+        <v>-8.3725</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.51</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2091</v>
+        <v>1.1388</v>
       </c>
       <c r="J302" t="n">
-        <v>30.2275</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.49</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1688</v>
+        <v>1.1137</v>
       </c>
       <c r="J303" t="n">
-        <v>29.22</v>
+        <v>27.8425</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.32</v>
       </c>
       <c r="I304" t="n">
-        <v>0.798</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>19.95</v>
+        <v>20.5525</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.1</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2066</v>
+        <v>0.2865</v>
       </c>
       <c r="J305" t="n">
-        <v>5.165</v>
+        <v>7.1625</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.92</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4391</v>
+        <v>-0.3609</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.9775</v>
+        <v>-9.022500000000001</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.06</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2162</v>
+        <v>0.2089</v>
       </c>
       <c r="J307" t="n">
-        <v>5.405</v>
+        <v>5.2225</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.97</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0322</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.1975</v>
+        <v>-0.805</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0692</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.73</v>
+        <v>-1.7975</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.65</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.5536</v>
+        <v>-0.3646</v>
       </c>
       <c r="J310" t="n">
-        <v>-13.84</v>
+        <v>-9.115</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.62</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.3927</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.83</v>
+        <v>-9.817500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3494/event_3494_evp_summary.xlsx
+++ b/database/event/3494/event_3494_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2312</v>
+        <v>6.1822</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1538</v>
+        <v>1.1447</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1751</v>
+        <v>2.1901</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2312</v>
+        <v>6.1822</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8189</v>
+        <v>3.7249</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4123</v>
+        <v>2.4573</v>
       </c>
       <c r="H2" t="n">
-        <v>7.969</v>
+        <v>7.3955</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1435</v>
+        <v>3.9935</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4123</v>
+        <v>2.4573</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>131</v>
       </c>
       <c r="M2" t="n">
-        <v>6.555800000000001</v>
+        <v>6.4508</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6428</v>
+        <v>5.7825</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0448</v>
+        <v>1.0707</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9094</v>
+        <v>2.0081</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6428</v>
+        <v>5.7825</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0847</v>
+        <v>4.0914</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5581</v>
+        <v>1.6911</v>
       </c>
       <c r="H3" t="n">
-        <v>8.9055</v>
+        <v>8.604799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6305</v>
+        <v>4.6465</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5581</v>
+        <v>1.6911</v>
       </c>
       <c r="K3" t="n">
         <v>146</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>6.188599999999999</v>
+        <v>6.3376</v>
       </c>
       <c r="N3" t="n">
         <v>274</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1475</v>
+        <v>5.1923</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9614</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6858</v>
+        <v>1.7394</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1475</v>
+        <v>5.1923</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1373</v>
+        <v>4.0752</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0102</v>
+        <v>1.1171</v>
       </c>
       <c r="H4" t="n">
-        <v>9.0908</v>
+        <v>8.551399999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7268</v>
+        <v>4.6177</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0102</v>
+        <v>1.1171</v>
       </c>
       <c r="K4" t="n">
         <v>150</v>
@@ -621,7 +621,7 @@
         <v>59</v>
       </c>
       <c r="M4" t="n">
-        <v>5.737</v>
+        <v>5.7348</v>
       </c>
       <c r="N4" t="n">
         <v>209</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9439</v>
+        <v>4.8729</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9154</v>
+        <v>0.9023</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5939</v>
+        <v>1.594</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9439</v>
+        <v>4.8729</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7182</v>
+        <v>3.635</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2257</v>
+        <v>1.2379</v>
       </c>
       <c r="H5" t="n">
-        <v>7.6141</v>
+        <v>7.0992</v>
       </c>
       <c r="I5" t="n">
-        <v>3.959</v>
+        <v>3.8335</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2257</v>
+        <v>1.2379</v>
       </c>
       <c r="K5" t="n">
         <v>146</v>
@@ -667,7 +667,7 @@
         <v>128</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1847</v>
+        <v>5.0714</v>
       </c>
       <c r="N5" t="n">
         <v>274</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5424</v>
+        <v>4.4793</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8411</v>
+        <v>0.8294</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4127</v>
+        <v>1.4149</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5424</v>
+        <v>4.4793</v>
       </c>
       <c r="F6" t="n">
-        <v>4.31</v>
+        <v>4.2452</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2324</v>
+        <v>0.2341</v>
       </c>
       <c r="H6" t="n">
-        <v>9.6996</v>
+        <v>9.1122</v>
       </c>
       <c r="I6" t="n">
-        <v>5.0433</v>
+        <v>4.9205</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2324</v>
+        <v>0.2341</v>
       </c>
       <c r="K6" t="n">
         <v>153</v>
@@ -713,7 +713,7 @@
         <v>131</v>
       </c>
       <c r="M6" t="n">
-        <v>5.275700000000001</v>
+        <v>5.154599999999999</v>
       </c>
       <c r="N6" t="n">
         <v>284</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2377</v>
+        <v>4.1803</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7846</v>
+        <v>0.774</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2751</v>
+        <v>1.2788</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2377</v>
+        <v>4.1803</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8076</v>
+        <v>3.7359</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4301</v>
+        <v>0.4444</v>
       </c>
       <c r="H7" t="n">
-        <v>7.9294</v>
+        <v>7.432</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1229</v>
+        <v>4.0132</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4301</v>
+        <v>0.4444</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>4.553</v>
+        <v>4.4576</v>
       </c>
       <c r="N7" t="n">
         <v>200</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0832</v>
+        <v>4.0806</v>
       </c>
       <c r="C8" t="n">
-        <v>0.756</v>
+        <v>0.7556</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2053</v>
+        <v>1.2334</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0832</v>
+        <v>4.0806</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1536</v>
+        <v>3.066</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9296</v>
+        <v>1.0146</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6249</v>
+        <v>5.2217</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9247</v>
+        <v>2.8197</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9296</v>
+        <v>1.0146</v>
       </c>
       <c r="K8" t="n">
         <v>153</v>
@@ -805,7 +805,7 @@
         <v>131</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8543</v>
+        <v>3.8343</v>
       </c>
       <c r="N8" t="n">
         <v>284</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9506</v>
+        <v>3.9535</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7315</v>
+        <v>0.732</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1455</v>
+        <v>1.1755</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9506</v>
+        <v>3.9535</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2889</v>
+        <v>3.2282</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6617</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>6.1017</v>
+        <v>5.7569</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1726</v>
+        <v>3.1087</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6617</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>144</v>
@@ -851,7 +851,7 @@
         <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8343</v>
+        <v>3.834</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7198</v>
+        <v>3.7038</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6888</v>
+        <v>0.6858</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0413</v>
+        <v>1.0618</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7198</v>
+        <v>3.7038</v>
       </c>
       <c r="F10" t="n">
-        <v>3.431</v>
+        <v>3.369</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2888</v>
+        <v>0.3348</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6025</v>
+        <v>6.2214</v>
       </c>
       <c r="I10" t="n">
-        <v>3.433</v>
+        <v>3.3595</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2888</v>
+        <v>0.3348</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7218</v>
+        <v>3.6943</v>
       </c>
       <c r="N10" t="n">
         <v>200</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4162</v>
+        <v>3.3403</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6325</v>
+        <v>0.6185</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9042</v>
+        <v>0.8964</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4162</v>
+        <v>3.3403</v>
       </c>
       <c r="F11" t="n">
-        <v>3.272</v>
+        <v>3.2082</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1442</v>
+        <v>0.1321</v>
       </c>
       <c r="H11" t="n">
-        <v>6.0423</v>
+        <v>5.691</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1417</v>
+        <v>3.0731</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1442</v>
+        <v>0.1321</v>
       </c>
       <c r="K11" t="n">
         <v>150</v>
@@ -943,7 +943,7 @@
         <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2859</v>
+        <v>3.2052</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0805</v>
+        <v>3.0371</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5704</v>
+        <v>0.5623</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7527</v>
+        <v>0.7583</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0805</v>
+        <v>3.0371</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9947</v>
+        <v>2.9089</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0858</v>
+        <v>0.1282</v>
       </c>
       <c r="H12" t="n">
-        <v>5.0653</v>
+        <v>4.7032</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6337</v>
+        <v>2.5397</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0858</v>
+        <v>0.1282</v>
       </c>
       <c r="K12" t="n">
         <v>146</v>
@@ -989,7 +989,7 @@
         <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7195</v>
+        <v>2.6679</v>
       </c>
       <c r="N12" t="n">
         <v>274</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9983</v>
+        <v>2.9606</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5552</v>
+        <v>0.5482</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7156</v>
+        <v>0.7235</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9983</v>
+        <v>2.9606</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6484</v>
+        <v>1.5695</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3499</v>
+        <v>1.3911</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6484</v>
+        <v>1.5695</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8571</v>
+        <v>0.8475</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3499</v>
+        <v>1.3911</v>
       </c>
       <c r="K13" t="n">
         <v>146</v>
@@ -1035,7 +1035,7 @@
         <v>128</v>
       </c>
       <c r="M13" t="n">
-        <v>2.207</v>
+        <v>2.2386</v>
       </c>
       <c r="N13" t="n">
         <v>274</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9205</v>
+        <v>2.8141</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5211</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6804</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9205</v>
+        <v>2.8141</v>
       </c>
       <c r="F14" t="n">
-        <v>3.346</v>
+        <v>2.279</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4255</v>
+        <v>0.5351</v>
       </c>
       <c r="H14" t="n">
-        <v>6.3029</v>
+        <v>2.6252</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2772</v>
+        <v>1.4176</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4255</v>
+        <v>0.5351</v>
       </c>
       <c r="K14" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="L14" t="n">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8517</v>
+        <v>1.9527</v>
       </c>
       <c r="N14" t="n">
-        <v>200</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7823</v>
+        <v>2.7882</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5152</v>
+        <v>0.5163</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6181</v>
+        <v>0.645</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7823</v>
+        <v>2.7882</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3245</v>
+        <v>3.234</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4578</v>
+        <v>-0.4458</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7037</v>
+        <v>5.7758</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4058</v>
+        <v>3.1189</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4578</v>
+        <v>-0.4458</v>
       </c>
       <c r="K15" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="L15" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8636</v>
+        <v>2.6731</v>
       </c>
       <c r="N15" t="n">
-        <v>284</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6099</v>
+        <v>2.3917</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4832</v>
+        <v>0.4428</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5402</v>
+        <v>0.4645</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6099</v>
+        <v>2.3917</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6099</v>
+        <v>2.3917</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6099</v>
+        <v>2.5098</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6099</v>
+        <v>2.5098</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.6099</v>
+        <v>2.5098</v>
       </c>
       <c r="N16" t="n">
         <v>147</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4638</v>
+        <v>2.3692</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4562</v>
+        <v>0.4387</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4743</v>
+        <v>0.4543</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4638</v>
+        <v>2.3692</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7706</v>
+        <v>2.6972</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3068</v>
+        <v>-0.328</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2756</v>
+        <v>4.0049</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2231</v>
+        <v>2.1626</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3068</v>
+        <v>-0.328</v>
       </c>
       <c r="K17" t="n">
         <v>150</v>
@@ -1219,7 +1219,7 @@
         <v>59</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9163</v>
+        <v>1.8346</v>
       </c>
       <c r="N17" t="n">
         <v>209</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4093</v>
+        <v>2.3027</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4461</v>
+        <v>0.4264</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4497</v>
+        <v>0.424</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4093</v>
+        <v>2.3027</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4223</v>
+        <v>2.3184</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.013</v>
+        <v>-0.0157</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0485</v>
+        <v>2.755</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5851</v>
+        <v>1.4877</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.013</v>
+        <v>-0.0157</v>
       </c>
       <c r="K18" t="n">
         <v>144</v>
@@ -1265,7 +1265,7 @@
         <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5721</v>
+        <v>1.472</v>
       </c>
       <c r="N18" t="n">
         <v>200</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2775</v>
+        <v>2.1515</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4217</v>
+        <v>0.3984</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3902</v>
+        <v>0.3552</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2775</v>
+        <v>2.1515</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2775</v>
+        <v>2.1515</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2775</v>
+        <v>2.1515</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2775</v>
+        <v>2.1515</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2775</v>
+        <v>2.1515</v>
       </c>
       <c r="N19" t="n">
         <v>147</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2229</v>
+        <v>2.1224</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4116</v>
+        <v>0.393</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3655</v>
+        <v>0.342</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2229</v>
+        <v>2.1224</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2229</v>
+        <v>2.1224</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2229</v>
+        <v>2.1224</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2229</v>
+        <v>2.1224</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2229</v>
+        <v>2.1224</v>
       </c>
       <c r="N20" t="n">
         <v>147</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9474</v>
+        <v>1.8436</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3606</v>
+        <v>0.3414</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2411</v>
+        <v>0.215</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9474</v>
+        <v>1.8436</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9474</v>
+        <v>1.8436</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9474</v>
+        <v>1.8436</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9474</v>
+        <v>1.8436</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9474</v>
+        <v>1.8436</v>
       </c>
       <c r="N21" t="n">
         <v>167</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8737</v>
+        <v>1.7727</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3469</v>
+        <v>0.3282</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2079</v>
+        <v>0.1828</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8737</v>
+        <v>1.7727</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2716</v>
+        <v>2.1911</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3979</v>
+        <v>-0.4184</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5173</v>
+        <v>2.335</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3089</v>
+        <v>1.2609</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3979</v>
+        <v>-0.4184</v>
       </c>
       <c r="K22" t="n">
         <v>150</v>
@@ -1449,7 +1449,7 @@
         <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>0.911</v>
+        <v>0.8424999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>209</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>queztone</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6383</v>
+        <v>1.7068</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3033</v>
+        <v>0.316</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1016</v>
+        <v>0.1528</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6383</v>
+        <v>1.7068</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6383</v>
+        <v>-0.1378</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1.8446</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6383</v>
+        <v>-0.1378</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6383</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.8446</v>
       </c>
       <c r="K23" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6383</v>
+        <v>1.7702</v>
       </c>
       <c r="N23" t="n">
-        <v>167</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>queztone</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6027</v>
+        <v>1.5561</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2968</v>
+        <v>0.2881</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0842</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6027</v>
+        <v>1.5561</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1531</v>
+        <v>1.5561</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7558</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1531</v>
+        <v>1.5561</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0796</v>
+        <v>1.5561</v>
       </c>
       <c r="J24" t="n">
-        <v>1.7558</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L24" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6762</v>
+        <v>1.5561</v>
       </c>
       <c r="N24" t="n">
-        <v>284</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.399</v>
+        <v>1.307</v>
       </c>
       <c r="C25" t="n">
-        <v>0.259</v>
+        <v>0.242</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0064</v>
+        <v>-0.0292</v>
       </c>
       <c r="E25" t="n">
-        <v>1.399</v>
+        <v>1.307</v>
       </c>
       <c r="F25" t="n">
-        <v>1.399</v>
+        <v>1.307</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.399</v>
+        <v>1.307</v>
       </c>
       <c r="I25" t="n">
-        <v>1.399</v>
+        <v>1.307</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.399</v>
+        <v>1.307</v>
       </c>
       <c r="N25" t="n">
         <v>167</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.0895</v>
+        <v>0.9937</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2017</v>
+        <v>0.184</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1462</v>
+        <v>-0.1719</v>
       </c>
       <c r="E26" t="n">
-        <v>1.0895</v>
+        <v>0.9937</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0895</v>
+        <v>0.9937</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0895</v>
+        <v>0.9937</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0895</v>
+        <v>0.9937</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0895</v>
+        <v>0.9937</v>
       </c>
       <c r="N26" t="n">
         <v>167</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7226</v>
+        <v>0.9083</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1338</v>
+        <v>0.1682</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3118</v>
+        <v>-0.2107</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7226</v>
+        <v>0.9083</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7226</v>
+        <v>0.6435</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.2648</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7226</v>
+        <v>0.6435</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7226</v>
+        <v>0.3475</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.2648</v>
       </c>
       <c r="K27" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7226</v>
+        <v>0.6123</v>
       </c>
       <c r="N27" t="n">
-        <v>152</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6748</v>
+        <v>0.6321</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1249</v>
+        <v>0.117</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3334</v>
+        <v>-0.3365</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6748</v>
+        <v>0.6321</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4317</v>
+        <v>0.6321</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2431</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4317</v>
+        <v>0.6321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2245</v>
+        <v>0.6321</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2431</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L28" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4676</v>
+        <v>0.6321</v>
       </c>
       <c r="N28" t="n">
-        <v>274</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.445</v>
+        <v>0.425</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0824</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4371</v>
+        <v>-0.4307</v>
       </c>
       <c r="E29" t="n">
-        <v>0.445</v>
+        <v>0.425</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8037</v>
+        <v>0.8122</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3587</v>
+        <v>-0.3872</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8037</v>
+        <v>0.8122</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4179</v>
+        <v>0.4386</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3587</v>
+        <v>-0.3872</v>
       </c>
       <c r="K29" t="n">
         <v>150</v>
@@ -1771,7 +1771,7 @@
         <v>59</v>
       </c>
       <c r="M29" t="n">
-        <v>0.05919999999999997</v>
+        <v>0.0514</v>
       </c>
       <c r="N29" t="n">
         <v>209</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1572</v>
+        <v>0.0193</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0291</v>
+        <v>0.0036</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1572</v>
+        <v>0.0193</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1572</v>
+        <v>0.0193</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1572</v>
+        <v>0.0193</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1572</v>
+        <v>0.0193</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1572</v>
+        <v>0.0193</v>
       </c>
       <c r="N30" t="n">
         <v>147</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0939</v>
+        <v>-0.1611</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0174</v>
+        <v>-0.0298</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6804</v>
+        <v>-0.6975</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0939</v>
+        <v>-0.1611</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0939</v>
+        <v>-0.1611</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0939</v>
+        <v>-0.1611</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0939</v>
+        <v>-0.1611</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0939</v>
+        <v>-0.1611</v>
       </c>
       <c r="N31" t="n">
         <v>147</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2125</v>
+        <v>-0.203</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0393</v>
+        <v>-0.0376</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7339</v>
+        <v>-0.7166</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2125</v>
+        <v>-0.203</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2125</v>
+        <v>-0.203</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2125</v>
+        <v>-0.203</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2125</v>
+        <v>-0.203</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2125</v>
+        <v>-0.203</v>
       </c>
       <c r="N32" t="n">
         <v>167</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3079</v>
+        <v>-0.3616</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.057</v>
+        <v>-0.067</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.777</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3079</v>
+        <v>-0.3616</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3079</v>
+        <v>-0.3616</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3079</v>
+        <v>-0.3616</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3079</v>
+        <v>-0.3616</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3079</v>
+        <v>-0.3616</v>
       </c>
       <c r="N33" t="n">
         <v>152</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4863</v>
+        <v>-0.5799</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.09</v>
+        <v>-0.1074</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8576</v>
+        <v>-0.8882</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4863</v>
+        <v>-0.5799</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4863</v>
+        <v>-0.5799</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4863</v>
+        <v>-0.5799</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4863</v>
+        <v>-0.5799</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4863</v>
+        <v>-0.5799</v>
       </c>
       <c r="N34" t="n">
         <v>152</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5854</v>
+        <v>-0.6387</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1084</v>
+        <v>-0.1183</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9023</v>
+        <v>-0.915</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5854</v>
+        <v>-0.6387</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5854</v>
+        <v>-0.6387</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5854</v>
+        <v>-0.6387</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5854</v>
+        <v>-0.6387</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5854</v>
+        <v>-0.6387</v>
       </c>
       <c r="N35" t="n">
         <v>147</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9344</v>
+        <v>-1.0013</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.173</v>
+        <v>-0.1854</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0598</v>
+        <v>-1.08</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9344</v>
+        <v>-1.0013</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9344</v>
+        <v>-1.0013</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9344</v>
+        <v>-1.0013</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9344</v>
+        <v>-1.0013</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9344</v>
+        <v>-1.0013</v>
       </c>
       <c r="N36" t="n">
         <v>147</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0229</v>
+        <v>-1.1295</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1894</v>
+        <v>-0.2091</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0998</v>
+        <v>-1.1384</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0229</v>
+        <v>-1.1295</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0229</v>
+        <v>-1.1295</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0229</v>
+        <v>-1.1295</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0229</v>
+        <v>-1.1295</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0229</v>
+        <v>-1.1295</v>
       </c>
       <c r="N37" t="n">
         <v>152</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2184</v>
+        <v>-1.19</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2256</v>
+        <v>-0.2203</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1881</v>
+        <v>-1.1659</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2184</v>
+        <v>-1.19</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2184</v>
+        <v>-1.19</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2184</v>
+        <v>-1.19</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2184</v>
+        <v>-1.19</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2184</v>
+        <v>-1.19</v>
       </c>
       <c r="N38" t="n">
         <v>147</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2432</v>
+        <v>-1.3457</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2302</v>
+        <v>-0.2492</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1993</v>
+        <v>-1.2368</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2432</v>
+        <v>-1.3457</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2432</v>
+        <v>-1.3457</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2432</v>
+        <v>-1.3457</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2432</v>
+        <v>-1.3457</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2432</v>
+        <v>-1.3457</v>
       </c>
       <c r="N39" t="n">
         <v>147</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4352</v>
+        <v>-1.5078</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2657</v>
+        <v>-0.2792</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2859</v>
+        <v>-1.3106</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4352</v>
+        <v>-1.5078</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4352</v>
+        <v>-1.5078</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4352</v>
+        <v>-1.5078</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4352</v>
+        <v>-1.5078</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4352</v>
+        <v>-1.5078</v>
       </c>
       <c r="N40" t="n">
         <v>152</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8035</v>
+        <v>-1.9042</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3339</v>
+        <v>-0.3526</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4522</v>
+        <v>-1.491</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8035</v>
+        <v>-1.9042</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8035</v>
+        <v>-1.9042</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8035</v>
+        <v>-1.9042</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8035</v>
+        <v>-1.9042</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8035</v>
+        <v>-1.9042</v>
       </c>
       <c r="N41" t="n">
         <v>147</v>
@@ -2429,10 +2429,10 @@
         <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2157</v>
+        <v>0.2095</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1768</v>
+        <v>5.028</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0292</v>
+        <v>-0.0422</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7008</v>
+        <v>-1.0128</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0431</v>
+        <v>-0.0571</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0344</v>
+        <v>-1.3704</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.63</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3812</v>
+        <v>-0.3947</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.1488</v>
+        <v>-9.472799999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.54</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4648</v>
+        <v>-0.4742</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.1552</v>
+        <v>-11.3808</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2459</v>
+        <v>1.296</v>
       </c>
       <c r="J7" t="n">
-        <v>29.9016</v>
+        <v>31.104</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9056</v>
+        <v>0.8556</v>
       </c>
       <c r="J8" t="n">
-        <v>21.7344</v>
+        <v>20.5344</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.27</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7087</v>
+        <v>0.6813</v>
       </c>
       <c r="J9" t="n">
-        <v>17.0088</v>
+        <v>16.3512</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="J10" t="n">
-        <v>14.7936</v>
+        <v>14.376</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.98</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1661</v>
+        <v>-0.1498</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.9864</v>
+        <v>-3.5952</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8586</v>
+        <v>0.8512</v>
       </c>
       <c r="J12" t="n">
-        <v>15.4548</v>
+        <v>15.3216</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.58</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6622</v>
+        <v>0.669</v>
       </c>
       <c r="J13" t="n">
-        <v>11.9196</v>
+        <v>12.042</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5332</v>
+        <v>0.547</v>
       </c>
       <c r="J14" t="n">
-        <v>9.5976</v>
+        <v>9.846</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.36</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4376</v>
+        <v>0.456</v>
       </c>
       <c r="J15" t="n">
-        <v>7.8768</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.32</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3931</v>
+        <v>0.4134</v>
       </c>
       <c r="J16" t="n">
-        <v>7.0758</v>
+        <v>7.4412</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1619</v>
+        <v>0.1412</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9142</v>
+        <v>2.5416</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2732</v>
+        <v>-0.2951</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.9176</v>
+        <v>-5.3118</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.57</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4108</v>
+        <v>-0.4274</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.3944</v>
+        <v>-7.6932</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.52</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4576</v>
+        <v>-0.4714</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.236800000000001</v>
+        <v>-8.485200000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.48</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4952</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.913600000000001</v>
+        <v>-9.1188</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.26</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5732</v>
+        <v>0.5527</v>
       </c>
       <c r="J22" t="n">
-        <v>17.196</v>
+        <v>16.581</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0825</v>
+        <v>-0.0948</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.475</v>
+        <v>-2.844</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.85</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1802</v>
+        <v>-0.1955</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.406</v>
+        <v>-5.865</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1802</v>
+        <v>-0.1955</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.406</v>
+        <v>-5.865</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.77</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2608</v>
+        <v>-0.2756</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.824</v>
+        <v>-8.268000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0346</v>
+        <v>0.9797</v>
       </c>
       <c r="J27" t="n">
-        <v>31.038</v>
+        <v>29.391</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0346</v>
+        <v>0.9797</v>
       </c>
       <c r="J28" t="n">
-        <v>31.038</v>
+        <v>29.391</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3176</v>
+        <v>-0.3068</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.528</v>
+        <v>-9.204000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3767</v>
+        <v>-0.3613</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.301</v>
+        <v>-10.839</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4618</v>
+        <v>-0.439</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.854</v>
+        <v>-13.17</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.42</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7864</v>
+        <v>0.8649</v>
       </c>
       <c r="J32" t="n">
-        <v>23.592</v>
+        <v>25.947</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3889</v>
+        <v>0.4197</v>
       </c>
       <c r="J33" t="n">
-        <v>11.667</v>
+        <v>12.591</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1415</v>
+        <v>0.1533</v>
       </c>
       <c r="J34" t="n">
-        <v>4.245</v>
+        <v>4.599</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.99</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0803</v>
+        <v>-0.0772</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.409</v>
+        <v>-2.316</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1935</v>
+        <v>-0.189</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.805</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.39</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5865</v>
+        <v>0.654</v>
       </c>
       <c r="J37" t="n">
-        <v>17.595</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.98</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0377</v>
+        <v>-0.044</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.131</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0519</v>
+        <v>-0.0596</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.557</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.91</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1252</v>
+        <v>-0.1371</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.756</v>
+        <v>-4.113</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1902</v>
+        <v>-0.2033</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.706</v>
+        <v>-6.099</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7943</v>
+        <v>0.8797</v>
       </c>
       <c r="J42" t="n">
-        <v>23.0347</v>
+        <v>25.5113</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7039</v>
+        <v>0.7815</v>
       </c>
       <c r="J43" t="n">
-        <v>20.4131</v>
+        <v>22.6635</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5985</v>
+        <v>0.6657</v>
       </c>
       <c r="J44" t="n">
-        <v>17.3565</v>
+        <v>19.3053</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.27</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5585</v>
+        <v>0.6212</v>
       </c>
       <c r="J45" t="n">
-        <v>16.1965</v>
+        <v>18.0148</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.659</v>
+        <v>-0.6092</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.111</v>
+        <v>-17.6668</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4237</v>
+        <v>0.4631</v>
       </c>
       <c r="J47" t="n">
-        <v>12.2873</v>
+        <v>13.4299</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2694</v>
+        <v>0.2692</v>
       </c>
       <c r="J48" t="n">
-        <v>7.8126</v>
+        <v>7.8068</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.86</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1685</v>
+        <v>-0.1839</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.8865</v>
+        <v>-5.3331</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.76</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2691</v>
+        <v>-0.284</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.8039</v>
+        <v>-8.236000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.346</v>
+        <v>-0.3588</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.034</v>
+        <v>-10.4052</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5113</v>
+        <v>0.5722</v>
       </c>
       <c r="J52" t="n">
-        <v>15.339</v>
+        <v>17.166</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1686</v>
+        <v>0.1809</v>
       </c>
       <c r="J53" t="n">
-        <v>5.058</v>
+        <v>5.427</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1686</v>
+        <v>0.1809</v>
       </c>
       <c r="J54" t="n">
-        <v>5.058</v>
+        <v>5.427</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1686</v>
+        <v>0.1809</v>
       </c>
       <c r="J55" t="n">
-        <v>5.058</v>
+        <v>5.427</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.95</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0861</v>
+        <v>-0.0939</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.583</v>
+        <v>-2.817</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.629</v>
+        <v>0.6893</v>
       </c>
       <c r="J57" t="n">
-        <v>18.87</v>
+        <v>20.679</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.11</v>
       </c>
       <c r="I58" t="n">
-        <v>0.354</v>
+        <v>0.3616</v>
       </c>
       <c r="J58" t="n">
-        <v>10.62</v>
+        <v>10.848</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2677</v>
+        <v>-0.2648</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.031000000000001</v>
+        <v>-7.944</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.91</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3277</v>
+        <v>-0.3207</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.831</v>
+        <v>-9.621</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3569</v>
+        <v>-0.3476</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.707</v>
+        <v>-10.428</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.28</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4931</v>
+        <v>0.5444</v>
       </c>
       <c r="J62" t="n">
-        <v>12.8206</v>
+        <v>14.1544</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2615</v>
+        <v>0.2635</v>
       </c>
       <c r="J63" t="n">
-        <v>6.799</v>
+        <v>6.851</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.85</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1816</v>
+        <v>-0.1966</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.7216</v>
+        <v>-5.1116</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2225</v>
+        <v>-0.2374</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.785</v>
+        <v>-6.1724</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3394</v>
+        <v>-0.3519</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.824400000000001</v>
+        <v>-9.1494</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7593</v>
+        <v>0.841</v>
       </c>
       <c r="J67" t="n">
-        <v>19.7418</v>
+        <v>21.866</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.3</v>
       </c>
       <c r="I68" t="n">
-        <v>0.601</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>15.626</v>
+        <v>17.3628</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4653</v>
+        <v>0.5157</v>
       </c>
       <c r="J69" t="n">
-        <v>12.0978</v>
+        <v>13.4082</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.14</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3764</v>
+        <v>0.406</v>
       </c>
       <c r="J70" t="n">
-        <v>9.7864</v>
+        <v>10.556</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1783</v>
+        <v>0.1956</v>
       </c>
       <c r="J71" t="n">
-        <v>4.6358</v>
+        <v>5.0856</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4441</v>
+        <v>1.4311</v>
       </c>
       <c r="J72" t="n">
-        <v>34.6584</v>
+        <v>34.3464</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.55</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1788</v>
+        <v>1.1492</v>
       </c>
       <c r="J73" t="n">
-        <v>28.2912</v>
+        <v>27.5808</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.34</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8568</v>
+        <v>0.8137</v>
       </c>
       <c r="J74" t="n">
-        <v>20.5632</v>
+        <v>19.5288</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1246</v>
+        <v>0.1501</v>
       </c>
       <c r="J75" t="n">
-        <v>2.9904</v>
+        <v>3.6024</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.87</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5152</v>
+        <v>-0.4766</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.3648</v>
+        <v>-11.4384</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.18</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4317</v>
+        <v>0.4213</v>
       </c>
       <c r="J77" t="n">
-        <v>10.3608</v>
+        <v>10.1112</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4123</v>
+        <v>0.4033</v>
       </c>
       <c r="J78" t="n">
-        <v>9.895200000000001</v>
+        <v>9.6792</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.77</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2586</v>
+        <v>-0.2738</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.2064</v>
+        <v>-6.5712</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2684</v>
+        <v>-0.2834</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.4416</v>
+        <v>-6.8016</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3262</v>
+        <v>-0.3398</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.8288</v>
+        <v>-8.155200000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0847</v>
+        <v>0.0013</v>
       </c>
       <c r="J82" t="n">
-        <v>1.5246</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.54</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.4063</v>
+        <v>-0.4288</v>
       </c>
       <c r="J83" t="n">
-        <v>-7.3134</v>
+        <v>-7.7184</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.47</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.4699</v>
+        <v>-0.4883</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.4582</v>
+        <v>-8.789400000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5829,10 +5829,10 @@
         <v>2.07</v>
       </c>
       <c r="I87" t="n">
-        <v>1.7036</v>
+        <v>1.7165</v>
       </c>
       <c r="J87" t="n">
-        <v>30.6648</v>
+        <v>30.897</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.9</v>
       </c>
       <c r="I88" t="n">
-        <v>1.5213</v>
+        <v>1.5248</v>
       </c>
       <c r="J88" t="n">
-        <v>27.3834</v>
+        <v>27.4464</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.74</v>
       </c>
       <c r="I89" t="n">
-        <v>1.3476</v>
+        <v>1.3402</v>
       </c>
       <c r="J89" t="n">
-        <v>24.2568</v>
+        <v>24.1236</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.52</v>
       </c>
       <c r="I90" t="n">
-        <v>1.1012</v>
+        <v>1.0742</v>
       </c>
       <c r="J90" t="n">
-        <v>19.8216</v>
+        <v>19.3356</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.18</v>
       </c>
       <c r="I91" t="n">
-        <v>0.415</v>
+        <v>0.4341</v>
       </c>
       <c r="J91" t="n">
-        <v>7.47</v>
+        <v>7.8138</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.38</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9544</v>
+        <v>0.8995</v>
       </c>
       <c r="J92" t="n">
-        <v>24.8144</v>
+        <v>23.387</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.27</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7126</v>
+        <v>0.6839</v>
       </c>
       <c r="J93" t="n">
-        <v>18.5276</v>
+        <v>17.7814</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.23</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6223</v>
+        <v>0.603</v>
       </c>
       <c r="J94" t="n">
-        <v>16.1798</v>
+        <v>15.678</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.21</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5749</v>
+        <v>0.5605</v>
       </c>
       <c r="J95" t="n">
-        <v>14.9474</v>
+        <v>14.573</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.19</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5262</v>
+        <v>0.5168</v>
       </c>
       <c r="J96" t="n">
-        <v>13.6812</v>
+        <v>13.4368</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.09</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2928</v>
+        <v>0.2817</v>
       </c>
       <c r="J97" t="n">
-        <v>7.6128</v>
+        <v>7.3242</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.125</v>
+        <v>-0.1427</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.25</v>
+        <v>-3.7102</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2072</v>
+        <v>-0.2256</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.3872</v>
+        <v>-5.8656</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.71</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.303</v>
+        <v>-0.3199</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.878</v>
+        <v>-8.317399999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4346</v>
+        <v>-0.446</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.2996</v>
+        <v>-11.596</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6922</v>
+        <v>0.6606</v>
       </c>
       <c r="J102" t="n">
-        <v>19.3816</v>
+        <v>18.4968</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.18</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5214</v>
+        <v>0.508</v>
       </c>
       <c r="J103" t="n">
-        <v>14.5992</v>
+        <v>14.224</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4464</v>
+        <v>0.4399</v>
       </c>
       <c r="J104" t="n">
-        <v>12.4992</v>
+        <v>12.3172</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3152</v>
+        <v>0.319</v>
       </c>
       <c r="J105" t="n">
-        <v>8.8256</v>
+        <v>8.932</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.04</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1332</v>
+        <v>0.1475</v>
       </c>
       <c r="J106" t="n">
-        <v>3.7296</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.07</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2079</v>
+        <v>0.2093</v>
       </c>
       <c r="J107" t="n">
-        <v>5.8212</v>
+        <v>5.8604</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.99</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0118</v>
+        <v>-0.0186</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.3304</v>
+        <v>-0.5208</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1673</v>
+        <v>-0.1831</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.6844</v>
+        <v>-5.1268</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1982</v>
+        <v>-0.2141</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.5496</v>
+        <v>-5.9948</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2184</v>
+        <v>-0.2342</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.1152</v>
+        <v>-6.5576</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1809</v>
+        <v>0.184</v>
       </c>
       <c r="J112" t="n">
-        <v>4.7034</v>
+        <v>4.784</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0138</v>
+        <v>0.0098</v>
       </c>
       <c r="J113" t="n">
-        <v>0.3588</v>
+        <v>0.2548</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0698</v>
+        <v>-0.0815</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.8148</v>
+        <v>-2.119</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1155</v>
+        <v>-0.1296</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.003</v>
+        <v>-3.3696</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.71</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3179</v>
+        <v>-0.3315</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.2654</v>
+        <v>-8.619</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9584</v>
+        <v>0.8988</v>
       </c>
       <c r="J117" t="n">
-        <v>24.9184</v>
+        <v>23.3688</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6843</v>
+        <v>0.6551</v>
       </c>
       <c r="J118" t="n">
-        <v>17.7918</v>
+        <v>17.0326</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6127</v>
+        <v>0.5914</v>
       </c>
       <c r="J119" t="n">
-        <v>15.9302</v>
+        <v>15.3764</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2217</v>
+        <v>0.2334</v>
       </c>
       <c r="J120" t="n">
-        <v>5.7642</v>
+        <v>6.0684</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2433</v>
+        <v>-0.2323</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.3258</v>
+        <v>-6.0398</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4933</v>
+        <v>0.4842</v>
       </c>
       <c r="J122" t="n">
-        <v>14.799</v>
+        <v>14.526</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.457</v>
+        <v>0.4507</v>
       </c>
       <c r="J123" t="n">
-        <v>13.71</v>
+        <v>13.521</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.04</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1161</v>
+        <v>0.1246</v>
       </c>
       <c r="J124" t="n">
-        <v>3.483</v>
+        <v>3.738</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1117</v>
+        <v>-0.1236</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.351</v>
+        <v>-3.708</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4292</v>
+        <v>-0.4372</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.876</v>
+        <v>-13.116</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.63</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3409</v>
+        <v>1.3107</v>
       </c>
       <c r="J127" t="n">
-        <v>40.227</v>
+        <v>39.321</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2093</v>
+        <v>0.217</v>
       </c>
       <c r="J128" t="n">
-        <v>6.279</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1171</v>
+        <v>-0.1157</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.513</v>
+        <v>-3.471</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2548</v>
+        <v>-0.2483</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.644</v>
+        <v>-7.449</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4883</v>
+        <v>-0.4632</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.649</v>
+        <v>-13.896</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0049</v>
+        <v>0.945</v>
       </c>
       <c r="J132" t="n">
-        <v>26.1274</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7168</v>
+        <v>0.6822</v>
       </c>
       <c r="J133" t="n">
-        <v>18.6368</v>
+        <v>17.7372</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3963</v>
+        <v>0.3937</v>
       </c>
       <c r="J134" t="n">
-        <v>10.3038</v>
+        <v>10.2362</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1337</v>
+        <v>0.1478</v>
       </c>
       <c r="J135" t="n">
-        <v>3.4762</v>
+        <v>3.8428</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4173</v>
+        <v>-0.396</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.8498</v>
+        <v>-10.296</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3095</v>
+        <v>0.3032</v>
       </c>
       <c r="J137" t="n">
-        <v>8.047000000000001</v>
+        <v>7.8832</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1994</v>
+        <v>0.1975</v>
       </c>
       <c r="J138" t="n">
-        <v>5.1844</v>
+        <v>5.135</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.83</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1935</v>
+        <v>-0.2105</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.031</v>
+        <v>-5.473</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2431</v>
+        <v>-0.2598</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.3206</v>
+        <v>-6.7548</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.433</v>
+        <v>-0.4432</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.258</v>
+        <v>-11.5232</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.185</v>
+        <v>1.1499</v>
       </c>
       <c r="J142" t="n">
-        <v>31.995</v>
+        <v>31.0473</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.39</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9936</v>
+        <v>0.9351</v>
       </c>
       <c r="J143" t="n">
-        <v>26.8272</v>
+        <v>25.2477</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4153</v>
+        <v>0.4128</v>
       </c>
       <c r="J144" t="n">
-        <v>11.2131</v>
+        <v>11.1456</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0524</v>
+        <v>0.0711</v>
       </c>
       <c r="J145" t="n">
-        <v>1.4148</v>
+        <v>1.9197</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6182</v>
+        <v>-0.5755</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.6914</v>
+        <v>-15.5385</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5746</v>
+        <v>0.5506</v>
       </c>
       <c r="J147" t="n">
-        <v>15.5142</v>
+        <v>14.8662</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.119</v>
+        <v>0.1197</v>
       </c>
       <c r="J148" t="n">
-        <v>3.213</v>
+        <v>3.2319</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2159</v>
+        <v>-0.2323</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.8293</v>
+        <v>-6.2721</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2259</v>
+        <v>-0.2422</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.0993</v>
+        <v>-6.5394</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4447</v>
+        <v>-0.4539</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.0069</v>
+        <v>-12.2553</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0885</v>
+        <v>-0.1059</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.5665</v>
+        <v>-3.0711</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1561</v>
+        <v>-0.1745</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.5269</v>
+        <v>-5.0605</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.86</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1561</v>
+        <v>-0.1745</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.5269</v>
+        <v>-5.0605</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.187</v>
+        <v>-0.2056</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.423</v>
+        <v>-5.9624</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4518</v>
+        <v>-0.4625</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.1022</v>
+        <v>-13.4125</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.67</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3318</v>
+        <v>1.3112</v>
       </c>
       <c r="J157" t="n">
-        <v>38.6222</v>
+        <v>38.0248</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1102</v>
+        <v>1.0741</v>
       </c>
       <c r="J158" t="n">
-        <v>32.1958</v>
+        <v>31.1489</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.39</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9665</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>28.0285</v>
+        <v>26.4712</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1634</v>
+        <v>0.1852</v>
       </c>
       <c r="J160" t="n">
-        <v>4.7386</v>
+        <v>5.3708</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.82</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6427</v>
+        <v>-0.5928</v>
       </c>
       <c r="J161" t="n">
-        <v>-18.6383</v>
+        <v>-17.1912</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.73</v>
       </c>
       <c r="I162" t="n">
-        <v>1.359</v>
+        <v>1.3479</v>
       </c>
       <c r="J162" t="n">
-        <v>28.539</v>
+        <v>28.3059</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.64</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2557</v>
+        <v>1.2376</v>
       </c>
       <c r="J163" t="n">
-        <v>26.3697</v>
+        <v>25.9896</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.61</v>
       </c>
       <c r="I164" t="n">
-        <v>1.221</v>
+        <v>1.2004</v>
       </c>
       <c r="J164" t="n">
-        <v>25.641</v>
+        <v>25.2084</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.58</v>
       </c>
       <c r="I165" t="n">
-        <v>1.1863</v>
+        <v>1.163</v>
       </c>
       <c r="J165" t="n">
-        <v>24.9123</v>
+        <v>24.423</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.95</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.316</v>
+        <v>-0.2834</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.636</v>
+        <v>-5.9514</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.83</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1518</v>
+        <v>-0.1782</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.1878</v>
+        <v>-3.7422</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.74</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2487</v>
+        <v>-0.2723</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.2227</v>
+        <v>-5.7183</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.67</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3173</v>
+        <v>-0.3383</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.6633</v>
+        <v>-7.1043</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.52</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.454</v>
+        <v>-0.4686</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.534000000000001</v>
+        <v>-9.8406</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.45</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.52</v>
+        <v>-0.5302</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.92</v>
+        <v>-11.1342</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.85</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1156</v>
+        <v>-0.1452</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.9652</v>
+        <v>-2.4684</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.78</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1958</v>
+        <v>-0.2231</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.3286</v>
+        <v>-3.7927</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.54</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4287</v>
+        <v>-0.4459</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.2879</v>
+        <v>-7.5803</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4567</v>
+        <v>-0.4722</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.7639</v>
+        <v>-8.0274</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.35</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6089</v>
+        <v>-0.6132</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.3513</v>
+        <v>-10.4244</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.83</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4733</v>
+        <v>1.4688</v>
       </c>
       <c r="J177" t="n">
-        <v>25.0461</v>
+        <v>24.9696</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.67</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2908</v>
+        <v>1.2751</v>
       </c>
       <c r="J178" t="n">
-        <v>21.9436</v>
+        <v>21.6767</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.46</v>
       </c>
       <c r="I179" t="n">
-        <v>1.0468</v>
+        <v>1.007</v>
       </c>
       <c r="J179" t="n">
-        <v>17.7956</v>
+        <v>17.119</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.45</v>
       </c>
       <c r="I180" t="n">
-        <v>1.0337</v>
+        <v>0.9916</v>
       </c>
       <c r="J180" t="n">
-        <v>17.5729</v>
+        <v>16.8572</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.08</v>
       </c>
       <c r="I181" t="n">
-        <v>0.1784</v>
+        <v>0.2102</v>
       </c>
       <c r="J181" t="n">
-        <v>3.0328</v>
+        <v>3.5734</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.46</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9406</v>
+        <v>0.8811</v>
       </c>
       <c r="J182" t="n">
-        <v>27.2774</v>
+        <v>25.5519</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2342</v>
+        <v>0.2337</v>
       </c>
       <c r="J183" t="n">
-        <v>6.7918</v>
+        <v>6.7773</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.74</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2858</v>
+        <v>-0.3009</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.2882</v>
+        <v>-8.726100000000001</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3242</v>
+        <v>-0.3382</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.4018</v>
+        <v>-9.8078</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4913</v>
+        <v>-0.4979</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.2477</v>
+        <v>-14.4391</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.48</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1035</v>
+        <v>1.0655</v>
       </c>
       <c r="J187" t="n">
-        <v>32.0015</v>
+        <v>30.8995</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.47</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0908</v>
+        <v>1.0512</v>
       </c>
       <c r="J188" t="n">
-        <v>31.6332</v>
+        <v>30.4848</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.35</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8915</v>
+        <v>0.8417</v>
       </c>
       <c r="J189" t="n">
-        <v>25.8535</v>
+        <v>24.4093</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.35</v>
       </c>
       <c r="I190" t="n">
-        <v>0.8915</v>
+        <v>0.8417</v>
       </c>
       <c r="J190" t="n">
-        <v>25.8535</v>
+        <v>24.4093</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.1024</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>-31.9696</v>
+        <v>-28.9275</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.3</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6509</v>
+        <v>0.6223</v>
       </c>
       <c r="J192" t="n">
-        <v>16.9234</v>
+        <v>16.1798</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3511</v>
+        <v>0.3466</v>
       </c>
       <c r="J193" t="n">
-        <v>9.1286</v>
+        <v>9.0116</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.08</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2267</v>
+        <v>0.2282</v>
       </c>
       <c r="J194" t="n">
-        <v>5.8942</v>
+        <v>5.9332</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3648</v>
+        <v>-0.3769</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.4848</v>
+        <v>-9.7994</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.43</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5745</v>
+        <v>-0.5759</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.937</v>
+        <v>-14.9734</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.95</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6666</v>
+        <v>1.6626</v>
       </c>
       <c r="J197" t="n">
-        <v>43.3316</v>
+        <v>43.2276</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.4</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9859</v>
+        <v>0.9323</v>
       </c>
       <c r="J198" t="n">
-        <v>25.6334</v>
+        <v>24.2398</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.14</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3932</v>
+        <v>0.3975</v>
       </c>
       <c r="J199" t="n">
-        <v>10.2232</v>
+        <v>10.335</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0472</v>
       </c>
       <c r="J200" t="n">
-        <v>-1.7706</v>
+        <v>-1.2272</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3934</v>
+        <v>-0.3667</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.2284</v>
+        <v>-9.5342</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.59</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2342</v>
+        <v>1.2073</v>
       </c>
       <c r="J202" t="n">
-        <v>25.9182</v>
+        <v>25.3533</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9473</v>
+        <v>0.894</v>
       </c>
       <c r="J203" t="n">
-        <v>19.8933</v>
+        <v>18.774</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.27</v>
       </c>
       <c r="I204" t="n">
-        <v>0.709</v>
+        <v>0.6815</v>
       </c>
       <c r="J204" t="n">
-        <v>14.889</v>
+        <v>14.3115</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.2</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5445</v>
+        <v>0.5346</v>
       </c>
       <c r="J205" t="n">
-        <v>11.4345</v>
+        <v>11.2266</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.99</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1245</v>
+        <v>-0.1081</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.6145</v>
+        <v>-2.2701</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.01</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1309</v>
+        <v>0.1114</v>
       </c>
       <c r="J207" t="n">
-        <v>2.7489</v>
+        <v>2.3394</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1649</v>
+        <v>-0.1862</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.4629</v>
+        <v>-3.9102</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.76</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2464</v>
+        <v>-0.2665</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.1744</v>
+        <v>-5.5965</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.74</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.265</v>
+        <v>-0.2849</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.565</v>
+        <v>-5.9829</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.32</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6546</v>
+        <v>-0.653</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.7466</v>
+        <v>-13.713</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.48</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9216</v>
+        <v>0.8709</v>
       </c>
       <c r="J212" t="n">
-        <v>25.8048</v>
+        <v>24.3852</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1845</v>
+        <v>0.1922</v>
       </c>
       <c r="J213" t="n">
-        <v>5.166</v>
+        <v>5.3816</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0925</v>
+        <v>0.1005</v>
       </c>
       <c r="J214" t="n">
-        <v>2.59</v>
+        <v>2.814</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.84</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1979</v>
+        <v>-0.2115</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.5412</v>
+        <v>-5.922</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4652</v>
+        <v>-0.4716</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.0256</v>
+        <v>-13.2048</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.36</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9432</v>
+        <v>0.8832</v>
       </c>
       <c r="J217" t="n">
-        <v>26.4096</v>
+        <v>24.7296</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.29</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7834</v>
+        <v>0.7416</v>
       </c>
       <c r="J218" t="n">
-        <v>21.9352</v>
+        <v>20.7648</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.11</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3403</v>
+        <v>0.3427</v>
       </c>
       <c r="J219" t="n">
-        <v>9.5284</v>
+        <v>9.595599999999999</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.1</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3126</v>
+        <v>0.3172</v>
       </c>
       <c r="J220" t="n">
-        <v>8.752800000000001</v>
+        <v>8.881600000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.92</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3331</v>
+        <v>-0.3176</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.3268</v>
+        <v>-8.892799999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.93</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.0611</v>
+        <v>-0.0814</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.2831</v>
+        <v>-1.7094</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.76</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2469</v>
+        <v>-0.2669</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.1849</v>
+        <v>-5.6049</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.71</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2925</v>
+        <v>-0.3118</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.1425</v>
+        <v>-6.5478</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.7</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3018</v>
+        <v>-0.3208</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.3378</v>
+        <v>-6.7368</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.59</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4047</v>
+        <v>-0.4195</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.498699999999999</v>
+        <v>-8.8095</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.92</v>
       </c>
       <c r="I227" t="n">
-        <v>1.58</v>
+        <v>1.5802</v>
       </c>
       <c r="J227" t="n">
-        <v>33.18</v>
+        <v>33.1842</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>1.1664</v>
+        <v>1.1409</v>
       </c>
       <c r="J228" t="n">
-        <v>24.4944</v>
+        <v>23.9589</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.42</v>
       </c>
       <c r="I229" t="n">
-        <v>0.9919</v>
+        <v>0.9449</v>
       </c>
       <c r="J229" t="n">
-        <v>20.8299</v>
+        <v>19.8429</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.36</v>
       </c>
       <c r="I230" t="n">
-        <v>0.875</v>
+        <v>0.8346</v>
       </c>
       <c r="J230" t="n">
-        <v>18.375</v>
+        <v>17.5266</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.1</v>
       </c>
       <c r="I231" t="n">
-        <v>0.2416</v>
+        <v>0.2677</v>
       </c>
       <c r="J231" t="n">
-        <v>5.0736</v>
+        <v>5.6217</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.46</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8838</v>
+        <v>0.8375</v>
       </c>
       <c r="J232" t="n">
-        <v>26.514</v>
+        <v>25.125</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.089</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.67</v>
+        <v>-2.988</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1125</v>
+        <v>-0.1243</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.375</v>
+        <v>-3.729</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.87</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1678</v>
+        <v>-0.1809</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.034</v>
+        <v>-5.427</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.1889</v>
+        <v>-0.2022</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.667</v>
+        <v>-6.066</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.32</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8729</v>
+        <v>0.8166</v>
       </c>
       <c r="J237" t="n">
-        <v>26.187</v>
+        <v>24.498</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.29</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8017</v>
+        <v>0.7544</v>
       </c>
       <c r="J238" t="n">
-        <v>24.051</v>
+        <v>22.632</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.1</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3227</v>
+        <v>0.324</v>
       </c>
       <c r="J239" t="n">
-        <v>9.680999999999999</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2575</v>
+        <v>-0.2502</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.725</v>
+        <v>-7.506</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.87</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4634</v>
+        <v>-0.4402</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.902</v>
+        <v>-13.206</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3254</v>
+        <v>0.3104</v>
       </c>
       <c r="J242" t="n">
-        <v>7.4842</v>
+        <v>7.1392</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.86</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1545</v>
+        <v>-0.1733</v>
       </c>
       <c r="J243" t="n">
-        <v>-3.5535</v>
+        <v>-3.9859</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.74</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2716</v>
+        <v>-0.2899</v>
       </c>
       <c r="J244" t="n">
-        <v>-6.2468</v>
+        <v>-6.6677</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.66</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3475</v>
+        <v>-0.3634</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.9925</v>
+        <v>-8.3582</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.61</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3945</v>
+        <v>-0.4083</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.073499999999999</v>
+        <v>-9.3909</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.63</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2709</v>
+        <v>1.2486</v>
       </c>
       <c r="J247" t="n">
-        <v>29.2307</v>
+        <v>28.7178</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.56</v>
       </c>
       <c r="I248" t="n">
-        <v>1.1861</v>
+        <v>1.158</v>
       </c>
       <c r="J248" t="n">
-        <v>27.2803</v>
+        <v>26.634</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.31</v>
       </c>
       <c r="I249" t="n">
-        <v>0.789</v>
+        <v>0.7544</v>
       </c>
       <c r="J249" t="n">
-        <v>18.147</v>
+        <v>17.3512</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.15</v>
       </c>
       <c r="I250" t="n">
-        <v>0.4056</v>
+        <v>0.4118</v>
       </c>
       <c r="J250" t="n">
-        <v>9.328799999999999</v>
+        <v>9.471399999999999</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.06</v>
       </c>
       <c r="I251" t="n">
-        <v>0.1505</v>
+        <v>0.1762</v>
       </c>
       <c r="J251" t="n">
-        <v>3.4615</v>
+        <v>4.0526</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.11</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2931</v>
+        <v>0.2912</v>
       </c>
       <c r="J252" t="n">
-        <v>7.6206</v>
+        <v>7.5712</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.08</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2293</v>
+        <v>0.2302</v>
       </c>
       <c r="J253" t="n">
-        <v>5.9618</v>
+        <v>5.9852</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.86</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1676</v>
+        <v>-0.1832</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.3576</v>
+        <v>-4.7632</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.78</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2485</v>
+        <v>-0.2639</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.461</v>
+        <v>-6.8614</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.74</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2876</v>
+        <v>-0.3023</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.4776</v>
+        <v>-7.8598</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.51</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1462</v>
+        <v>1.1108</v>
       </c>
       <c r="J257" t="n">
-        <v>29.8012</v>
+        <v>28.8808</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0131</v>
+        <v>0.9593</v>
       </c>
       <c r="J258" t="n">
-        <v>26.3406</v>
+        <v>24.9418</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.14</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4036</v>
+        <v>0.4048</v>
       </c>
       <c r="J259" t="n">
-        <v>10.4936</v>
+        <v>10.5248</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2659</v>
+        <v>0.2782</v>
       </c>
       <c r="J260" t="n">
-        <v>6.9134</v>
+        <v>7.2332</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.02</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0389</v>
+        <v>0.0618</v>
       </c>
       <c r="J261" t="n">
-        <v>1.0114</v>
+        <v>1.6068</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.69</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4084</v>
+        <v>1.3833</v>
       </c>
       <c r="J262" t="n">
-        <v>30.9848</v>
+        <v>30.4326</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.29</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7964</v>
+        <v>0.7507</v>
       </c>
       <c r="J263" t="n">
-        <v>17.5208</v>
+        <v>16.5154</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2613</v>
+        <v>-0.2528</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.7486</v>
+        <v>-5.5616</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.85</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5221</v>
+        <v>-0.4924</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.4862</v>
+        <v>-10.8328</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.82</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.5643</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.2506</v>
+        <v>-12.4146</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.21</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4905</v>
+        <v>0.4753</v>
       </c>
       <c r="J267" t="n">
-        <v>10.791</v>
+        <v>10.4566</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.87</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1569</v>
+        <v>-0.1725</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.4518</v>
+        <v>-3.795</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.188</v>
+        <v>-0.2038</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.136</v>
+        <v>-4.4836</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.82</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2083</v>
+        <v>-0.2242</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.5826</v>
+        <v>-4.9324</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.82</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2083</v>
+        <v>-0.2242</v>
       </c>
       <c r="J271" t="n">
-        <v>-4.5826</v>
+        <v>-4.9324</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5134</v>
+        <v>0.5022</v>
       </c>
       <c r="J272" t="n">
-        <v>15.402</v>
+        <v>15.066</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.13</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3079</v>
+        <v>0.3108</v>
       </c>
       <c r="J273" t="n">
-        <v>9.237</v>
+        <v>9.324</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.04</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1172</v>
+        <v>0.1254</v>
       </c>
       <c r="J274" t="n">
-        <v>3.516</v>
+        <v>3.762</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.85</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1873</v>
+        <v>-0.2009</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.619</v>
+        <v>-6.027</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3261</v>
+        <v>-0.3379</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.782999999999999</v>
+        <v>-10.137</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.29</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5679</v>
+        <v>0.5582</v>
       </c>
       <c r="J277" t="n">
-        <v>17.037</v>
+        <v>16.746</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.18</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3766</v>
+        <v>0.381</v>
       </c>
       <c r="J278" t="n">
-        <v>11.298</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2662</v>
+        <v>0.2762</v>
       </c>
       <c r="J279" t="n">
-        <v>7.986</v>
+        <v>8.286</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J280" t="n">
-        <v>2.331</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.87</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.1777</v>
+        <v>-0.1886</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.331</v>
+        <v>-5.658</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.12</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3478</v>
+        <v>0.3358</v>
       </c>
       <c r="J282" t="n">
-        <v>8.695</v>
+        <v>8.395</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.11</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3266</v>
+        <v>0.3158</v>
       </c>
       <c r="J283" t="n">
-        <v>8.164999999999999</v>
+        <v>7.895</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.77</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.248</v>
+        <v>-0.2656</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.2</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.6</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4095</v>
+        <v>-0.4217</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.2375</v>
+        <v>-10.5425</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.57</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4373</v>
+        <v>-0.4481</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.9325</v>
+        <v>-11.2025</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.59</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2278</v>
+        <v>1.2016</v>
       </c>
       <c r="J287" t="n">
-        <v>30.695</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.33</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8353</v>
+        <v>0.7947</v>
       </c>
       <c r="J288" t="n">
-        <v>20.8825</v>
+        <v>19.8675</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.31</v>
       </c>
       <c r="I289" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7569</v>
       </c>
       <c r="J289" t="n">
-        <v>19.82</v>
+        <v>18.9225</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.31</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7569</v>
       </c>
       <c r="J290" t="n">
-        <v>19.82</v>
+        <v>18.9225</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I291" t="n">
-        <v>0.0914</v>
+        <v>0.1184</v>
       </c>
       <c r="J291" t="n">
-        <v>2.285</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1068</v>
+        <v>1.0711</v>
       </c>
       <c r="J292" t="n">
-        <v>27.67</v>
+        <v>26.7775</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.34</v>
       </c>
       <c r="I293" t="n">
-        <v>0.8589</v>
+        <v>0.8151</v>
       </c>
       <c r="J293" t="n">
-        <v>21.4725</v>
+        <v>20.3775</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.31</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.7577</v>
       </c>
       <c r="J294" t="n">
-        <v>19.8475</v>
+        <v>18.9425</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.26</v>
       </c>
       <c r="I295" t="n">
-        <v>0.6832</v>
+        <v>0.6592</v>
       </c>
       <c r="J295" t="n">
-        <v>17.08</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.12</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3339</v>
+        <v>0.3445</v>
       </c>
       <c r="J296" t="n">
-        <v>8.3475</v>
+        <v>8.612500000000001</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.07</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2364</v>
+        <v>0.2301</v>
       </c>
       <c r="J297" t="n">
-        <v>5.91</v>
+        <v>5.7525</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0945</v>
+        <v>-0.1105</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.3625</v>
+        <v>-2.7625</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2193</v>
+        <v>-0.2371</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.4825</v>
+        <v>-5.9275</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.72</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2968</v>
+        <v>-0.3132</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.42</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3349</v>
+        <v>-0.3501</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.3725</v>
+        <v>-8.7525</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.51</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1388</v>
+        <v>1.1043</v>
       </c>
       <c r="J302" t="n">
-        <v>28.47</v>
+        <v>27.6075</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.49</v>
       </c>
       <c r="I303" t="n">
-        <v>1.1137</v>
+        <v>1.0772</v>
       </c>
       <c r="J303" t="n">
-        <v>27.8425</v>
+        <v>26.93</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.32</v>
       </c>
       <c r="I304" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.7813</v>
       </c>
       <c r="J304" t="n">
-        <v>20.5525</v>
+        <v>19.5325</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.1</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2865</v>
+        <v>0.2991</v>
       </c>
       <c r="J305" t="n">
-        <v>7.1625</v>
+        <v>7.4775</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.92</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3609</v>
+        <v>-0.3371</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.022500000000001</v>
+        <v>-8.4275</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.06</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2089</v>
+        <v>0.2045</v>
       </c>
       <c r="J307" t="n">
-        <v>5.2225</v>
+        <v>5.1125</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.97</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0322</v>
+        <v>-0.0445</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.805</v>
+        <v>-1.1125</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0866</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.7975</v>
+        <v>-2.165</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.65</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3646</v>
+        <v>-0.3784</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.115</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.62</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3927</v>
+        <v>-0.4054</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.817500000000001</v>
+        <v>-10.135</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3494/event_3494_evp_summary.xlsx
+++ b/database/event/3494/event_3494_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1822</v>
+        <v>6.1698</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1447</v>
+        <v>1.1424</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1901</v>
+        <v>2.2049</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1822</v>
+        <v>6.1698</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7249</v>
+        <v>3.6593</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4573</v>
+        <v>2.5105</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3955</v>
+        <v>7.296</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9935</v>
+        <v>4.0965</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4573</v>
+        <v>2.5105</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>131</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4508</v>
+        <v>6.606999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7825</v>
+        <v>5.5699</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0707</v>
+        <v>1.0313</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0081</v>
+        <v>1.9316</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7825</v>
+        <v>5.5699</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0914</v>
+        <v>3.9352</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6911</v>
+        <v>1.6347</v>
       </c>
       <c r="H3" t="n">
-        <v>8.604799999999999</v>
+        <v>8.3317</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6465</v>
+        <v>4.678</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6911</v>
+        <v>1.6347</v>
       </c>
       <c r="K3" t="n">
         <v>146</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>6.3376</v>
+        <v>6.3127</v>
       </c>
       <c r="N3" t="n">
         <v>274</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1923</v>
+        <v>4.9514</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9614</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7394</v>
+        <v>1.6498</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1923</v>
+        <v>4.9514</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0752</v>
+        <v>3.913</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1171</v>
+        <v>1.0384</v>
       </c>
       <c r="H4" t="n">
-        <v>8.551399999999999</v>
+        <v>8.2485</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6177</v>
+        <v>4.6313</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1171</v>
+        <v>1.0384</v>
       </c>
       <c r="K4" t="n">
         <v>150</v>
@@ -621,7 +621,7 @@
         <v>59</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7348</v>
+        <v>5.669700000000001</v>
       </c>
       <c r="N4" t="n">
         <v>209</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8729</v>
+        <v>4.6503</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9023</v>
+        <v>0.861</v>
       </c>
       <c r="D5" t="n">
-        <v>1.594</v>
+        <v>1.5126</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8729</v>
+        <v>4.6503</v>
       </c>
       <c r="F5" t="n">
-        <v>3.635</v>
+        <v>3.5199</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2379</v>
+        <v>1.1304</v>
       </c>
       <c r="H5" t="n">
-        <v>7.0992</v>
+        <v>6.7726</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8335</v>
+        <v>3.8026</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2379</v>
+        <v>1.1304</v>
       </c>
       <c r="K5" t="n">
         <v>146</v>
@@ -667,7 +667,7 @@
         <v>128</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0714</v>
+        <v>4.933</v>
       </c>
       <c r="N5" t="n">
         <v>274</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4793</v>
+        <v>4.3328</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8294</v>
+        <v>0.8023</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4149</v>
+        <v>1.368</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4793</v>
+        <v>4.3328</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2452</v>
+        <v>4.0607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2341</v>
+        <v>0.2721</v>
       </c>
       <c r="H6" t="n">
-        <v>9.1122</v>
+        <v>8.803000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9205</v>
+        <v>4.9426</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2341</v>
+        <v>0.2721</v>
       </c>
       <c r="K6" t="n">
         <v>153</v>
@@ -713,7 +713,7 @@
         <v>131</v>
       </c>
       <c r="M6" t="n">
-        <v>5.154599999999999</v>
+        <v>5.2147</v>
       </c>
       <c r="N6" t="n">
         <v>284</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1803</v>
+        <v>4.0351</v>
       </c>
       <c r="C7" t="n">
-        <v>0.774</v>
+        <v>0.7471</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2788</v>
+        <v>1.2324</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1803</v>
+        <v>4.0351</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7359</v>
+        <v>3.0554</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4444</v>
+        <v>0.9797</v>
       </c>
       <c r="H7" t="n">
-        <v>7.432</v>
+        <v>5.0286</v>
       </c>
       <c r="I7" t="n">
-        <v>4.0132</v>
+        <v>2.8234</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4444</v>
+        <v>0.9797</v>
       </c>
       <c r="K7" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="L7" t="n">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4576</v>
+        <v>3.8031</v>
       </c>
       <c r="N7" t="n">
-        <v>200</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0806</v>
+        <v>3.9092</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7556</v>
+        <v>0.7238</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2334</v>
+        <v>1.175</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0806</v>
+        <v>3.9092</v>
       </c>
       <c r="F8" t="n">
-        <v>3.066</v>
+        <v>3.5481</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0146</v>
+        <v>0.3611</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2217</v>
+        <v>6.8784</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8197</v>
+        <v>3.862</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0146</v>
+        <v>0.3611</v>
       </c>
       <c r="K8" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="L8" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8343</v>
+        <v>4.223100000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>284</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9535</v>
+        <v>3.8507</v>
       </c>
       <c r="C9" t="n">
-        <v>0.732</v>
+        <v>0.713</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1755</v>
+        <v>1.1484</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9535</v>
+        <v>3.8507</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2282</v>
+        <v>3.1865</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.6642</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7569</v>
+        <v>5.5211</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1087</v>
+        <v>3.0999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.6642</v>
       </c>
       <c r="K9" t="n">
         <v>144</v>
@@ -851,7 +851,7 @@
         <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.834</v>
+        <v>3.7641</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7038</v>
+        <v>3.5719</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6858</v>
+        <v>0.6614</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0618</v>
+        <v>1.0214</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7038</v>
+        <v>3.5719</v>
       </c>
       <c r="F10" t="n">
-        <v>3.369</v>
+        <v>3.2439</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3348</v>
+        <v>0.328</v>
       </c>
       <c r="H10" t="n">
-        <v>6.2214</v>
+        <v>5.7364</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3595</v>
+        <v>3.2208</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3348</v>
+        <v>0.328</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6943</v>
+        <v>3.5488</v>
       </c>
       <c r="N10" t="n">
         <v>200</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3403</v>
+        <v>3.2505</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6185</v>
+        <v>0.6019</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8964</v>
+        <v>0.875</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3403</v>
+        <v>3.2505</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2082</v>
+        <v>3.1471</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1321</v>
+        <v>0.1034</v>
       </c>
       <c r="H11" t="n">
-        <v>5.691</v>
+        <v>5.3731</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0731</v>
+        <v>3.0168</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1321</v>
+        <v>0.1034</v>
       </c>
       <c r="K11" t="n">
         <v>150</v>
@@ -943,7 +943,7 @@
         <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2052</v>
+        <v>3.1202</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0371</v>
+        <v>2.9755</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5623</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7583</v>
+        <v>0.7497</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0371</v>
+        <v>2.9755</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9089</v>
+        <v>2.857</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1282</v>
+        <v>0.1185</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7032</v>
+        <v>4.2838</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5397</v>
+        <v>2.4052</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1282</v>
+        <v>0.1185</v>
       </c>
       <c r="K12" t="n">
         <v>146</v>
@@ -989,7 +989,7 @@
         <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6679</v>
+        <v>2.5237</v>
       </c>
       <c r="N12" t="n">
         <v>274</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9606</v>
+        <v>2.8833</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5482</v>
+        <v>0.5339</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7235</v>
+        <v>0.7077</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9606</v>
+        <v>2.8833</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5695</v>
+        <v>2.32</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3911</v>
+        <v>0.5633</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5695</v>
+        <v>2.32</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8475</v>
+        <v>1.3026</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3911</v>
+        <v>0.5633</v>
       </c>
       <c r="K13" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="L13" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2386</v>
+        <v>1.8659</v>
       </c>
       <c r="N13" t="n">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8141</v>
+        <v>2.7843</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5211</v>
+        <v>0.5155</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6626</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8141</v>
+        <v>2.7843</v>
       </c>
       <c r="F14" t="n">
-        <v>2.279</v>
+        <v>1.4898</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5351</v>
+        <v>1.2945</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6252</v>
+        <v>1.4898</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4176</v>
+        <v>0.8365</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5351</v>
+        <v>1.2945</v>
       </c>
       <c r="K14" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="L14" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9527</v>
+        <v>2.131</v>
       </c>
       <c r="N14" t="n">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7882</v>
+        <v>2.7269</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5163</v>
+        <v>0.5049</v>
       </c>
       <c r="D15" t="n">
-        <v>0.645</v>
+        <v>0.6364</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7882</v>
+        <v>2.7269</v>
       </c>
       <c r="F15" t="n">
-        <v>3.234</v>
+        <v>3.1411</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4458</v>
+        <v>-0.4142</v>
       </c>
       <c r="H15" t="n">
-        <v>5.7758</v>
+        <v>5.3506</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1189</v>
+        <v>3.0042</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4458</v>
+        <v>-0.4142</v>
       </c>
       <c r="K15" t="n">
         <v>144</v>
@@ -1127,7 +1127,7 @@
         <v>56</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6731</v>
+        <v>2.59</v>
       </c>
       <c r="N15" t="n">
         <v>200</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3917</v>
+        <v>2.4268</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4428</v>
+        <v>0.4493</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4645</v>
+        <v>0.4997</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3917</v>
+        <v>2.4268</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3917</v>
+        <v>2.7253</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.2985</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5098</v>
+        <v>3.7895</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5098</v>
+        <v>2.1277</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.2985</v>
       </c>
       <c r="K16" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5098</v>
+        <v>1.8292</v>
       </c>
       <c r="N16" t="n">
-        <v>147</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3692</v>
+        <v>2.4156</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4387</v>
+        <v>0.4473</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4543</v>
+        <v>0.4946</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3692</v>
+        <v>2.4156</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6972</v>
+        <v>2.4465</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.328</v>
+        <v>-0.0309</v>
       </c>
       <c r="H17" t="n">
-        <v>4.0049</v>
+        <v>2.7425</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1626</v>
+        <v>1.5398</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.328</v>
+        <v>-0.0309</v>
       </c>
       <c r="K17" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8346</v>
+        <v>1.5089</v>
       </c>
       <c r="N17" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3027</v>
+        <v>2.3351</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4264</v>
+        <v>0.4324</v>
       </c>
       <c r="D18" t="n">
-        <v>0.424</v>
+        <v>0.458</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3027</v>
+        <v>2.3351</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3184</v>
+        <v>2.3351</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0157</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.755</v>
+        <v>2.4013</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4877</v>
+        <v>2.4013</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0157</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.472</v>
+        <v>2.4013</v>
       </c>
       <c r="N18" t="n">
-        <v>200</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1515</v>
+        <v>2.1494</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3984</v>
+        <v>0.398</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3552</v>
+        <v>0.3734</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1515</v>
+        <v>2.1494</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1515</v>
+        <v>2.1494</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1515</v>
+        <v>2.1494</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1515</v>
+        <v>2.1494</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1515</v>
+        <v>2.1494</v>
       </c>
       <c r="N19" t="n">
         <v>147</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1224</v>
+        <v>2.1329</v>
       </c>
       <c r="C20" t="n">
-        <v>0.393</v>
+        <v>0.3949</v>
       </c>
       <c r="D20" t="n">
-        <v>0.342</v>
+        <v>0.3658</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1224</v>
+        <v>2.1329</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1224</v>
+        <v>2.1329</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1224</v>
+        <v>2.1329</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1224</v>
+        <v>2.1329</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1224</v>
+        <v>2.1329</v>
       </c>
       <c r="N20" t="n">
         <v>147</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DEV7L</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8436</v>
+        <v>1.9057</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3414</v>
+        <v>0.3529</v>
       </c>
       <c r="D21" t="n">
-        <v>0.215</v>
+        <v>0.2623</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8436</v>
+        <v>1.9057</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8436</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1.8405</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8436</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8436</v>
+        <v>0.0366</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.8405</v>
       </c>
       <c r="K21" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8436</v>
+        <v>1.8771</v>
       </c>
       <c r="N21" t="n">
-        <v>167</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7727</v>
+        <v>1.7921</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3282</v>
+        <v>0.3318</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1828</v>
+        <v>0.2106</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7727</v>
+        <v>1.7921</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1911</v>
+        <v>2.183</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4184</v>
+        <v>-0.3909</v>
       </c>
       <c r="H22" t="n">
-        <v>2.335</v>
+        <v>2.183</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2609</v>
+        <v>1.2257</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4184</v>
+        <v>-0.3909</v>
       </c>
       <c r="K22" t="n">
         <v>150</v>
@@ -1449,7 +1449,7 @@
         <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8424999999999999</v>
+        <v>0.8348</v>
       </c>
       <c r="N22" t="n">
         <v>209</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>DEV7L</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7068</v>
+        <v>1.7221</v>
       </c>
       <c r="C23" t="n">
-        <v>0.316</v>
+        <v>0.3189</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1528</v>
+        <v>0.1787</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7068</v>
+        <v>1.7221</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1378</v>
+        <v>1.7221</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8446</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1378</v>
+        <v>1.7221</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.07439999999999999</v>
+        <v>1.7221</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8446</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="L23" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7702</v>
+        <v>1.7221</v>
       </c>
       <c r="N23" t="n">
-        <v>284</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5561</v>
+        <v>1.47</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2881</v>
+        <v>0.2722</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0842</v>
+        <v>0.0639</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5561</v>
+        <v>1.47</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5561</v>
+        <v>1.47</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5561</v>
+        <v>1.47</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5561</v>
+        <v>1.47</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5561</v>
+        <v>1.47</v>
       </c>
       <c r="N24" t="n">
         <v>167</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.307</v>
+        <v>1.1523</v>
       </c>
       <c r="C25" t="n">
-        <v>0.242</v>
+        <v>0.2134</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0292</v>
+        <v>-0.0809</v>
       </c>
       <c r="E25" t="n">
-        <v>1.307</v>
+        <v>1.1523</v>
       </c>
       <c r="F25" t="n">
-        <v>1.307</v>
+        <v>1.1523</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.307</v>
+        <v>1.1523</v>
       </c>
       <c r="I25" t="n">
-        <v>1.307</v>
+        <v>1.1523</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.307</v>
+        <v>1.1523</v>
       </c>
       <c r="N25" t="n">
         <v>167</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZEDKO</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9937</v>
+        <v>0.9822</v>
       </c>
       <c r="C26" t="n">
-        <v>0.184</v>
+        <v>0.1819</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1719</v>
+        <v>-0.1583</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9937</v>
+        <v>0.9822</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9937</v>
+        <v>0.7833</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.1989</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9937</v>
+        <v>0.7833</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9937</v>
+        <v>0.4398</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.1989</v>
       </c>
       <c r="K26" t="n">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9937</v>
+        <v>0.6387</v>
       </c>
       <c r="N26" t="n">
-        <v>167</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>ZEDKO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9083</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1682</v>
+        <v>0.1742</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2107</v>
+        <v>-0.1771</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9083</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6435</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2648</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6435</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3475</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2648</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="L27" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6123</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>274</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6321</v>
+        <v>0.4988</v>
       </c>
       <c r="C28" t="n">
-        <v>0.117</v>
+        <v>0.0924</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3365</v>
+        <v>-0.3786</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6321</v>
+        <v>0.4988</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6321</v>
+        <v>0.4988</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6321</v>
+        <v>0.4988</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6321</v>
+        <v>0.4988</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6321</v>
+        <v>0.4988</v>
       </c>
       <c r="N28" t="n">
         <v>152</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.425</v>
+        <v>0.3982</v>
       </c>
       <c r="C29" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0737</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4307</v>
+        <v>-0.4244</v>
       </c>
       <c r="E29" t="n">
-        <v>0.425</v>
+        <v>0.3982</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8122</v>
+        <v>0.745</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3872</v>
+        <v>-0.3468</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8122</v>
+        <v>0.745</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4386</v>
+        <v>0.4183</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3872</v>
+        <v>-0.3468</v>
       </c>
       <c r="K29" t="n">
         <v>150</v>
@@ -1771,7 +1771,7 @@
         <v>59</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0514</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>209</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0193</v>
+        <v>-0.0382</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0036</v>
+        <v>-0.0071</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.6232</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0193</v>
+        <v>-0.0382</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0193</v>
+        <v>-0.0382</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0193</v>
+        <v>-0.0382</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0193</v>
+        <v>-0.0382</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0193</v>
+        <v>-0.0382</v>
       </c>
       <c r="N30" t="n">
         <v>147</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1611</v>
+        <v>-0.0592</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0298</v>
+        <v>-0.011</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6975</v>
+        <v>-0.6328</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1611</v>
+        <v>-0.0592</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1611</v>
+        <v>-0.0592</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1611</v>
+        <v>-0.0592</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1611</v>
+        <v>-0.0592</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1611</v>
+        <v>-0.0592</v>
       </c>
       <c r="N31" t="n">
         <v>147</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.203</v>
+        <v>-0.2537</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0376</v>
+        <v>-0.047</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7166</v>
+        <v>-0.7214</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.203</v>
+        <v>-0.2537</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.203</v>
+        <v>-0.2537</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.203</v>
+        <v>-0.2537</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.203</v>
+        <v>-0.2537</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.203</v>
+        <v>-0.2537</v>
       </c>
       <c r="N32" t="n">
         <v>167</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3616</v>
+        <v>-0.3865</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.067</v>
+        <v>-0.0716</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.7819</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3616</v>
+        <v>-0.3865</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3616</v>
+        <v>-0.3865</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3616</v>
+        <v>-0.3865</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3616</v>
+        <v>-0.3865</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3616</v>
+        <v>-0.3865</v>
       </c>
       <c r="N33" t="n">
         <v>152</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5799</v>
+        <v>-0.6292</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1074</v>
+        <v>-0.1165</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8882</v>
+        <v>-0.8924</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5799</v>
+        <v>-0.6292</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5799</v>
+        <v>-0.6292</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5799</v>
+        <v>-0.6292</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5799</v>
+        <v>-0.6292</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5799</v>
+        <v>-0.6292</v>
       </c>
       <c r="N34" t="n">
         <v>152</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6387</v>
+        <v>-0.721</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1183</v>
+        <v>-0.1335</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.915</v>
+        <v>-0.9342</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6387</v>
+        <v>-0.721</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6387</v>
+        <v>-0.721</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6387</v>
+        <v>-0.721</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6387</v>
+        <v>-0.721</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6387</v>
+        <v>-0.721</v>
       </c>
       <c r="N35" t="n">
         <v>147</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tomkeejs</t>
+          <t>tecek</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0013</v>
+        <v>-1.0005</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1854</v>
+        <v>-0.1853</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.08</v>
+        <v>-1.0616</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0013</v>
+        <v>-1.0005</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0013</v>
+        <v>-1.0005</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0013</v>
+        <v>-1.0005</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0013</v>
+        <v>-1.0005</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0013</v>
+        <v>-1.0005</v>
       </c>
       <c r="N36" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tecek</t>
+          <t>Tomkeejs</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1295</v>
+        <v>-1.0226</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2091</v>
+        <v>-0.1893</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1384</v>
+        <v>-1.0716</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1295</v>
+        <v>-1.0226</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1295</v>
+        <v>-1.0226</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1295</v>
+        <v>-1.0226</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1295</v>
+        <v>-1.0226</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1295</v>
+        <v>-1.0226</v>
       </c>
       <c r="N37" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.19</v>
+        <v>-1.1217</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2203</v>
+        <v>-0.2077</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1659</v>
+        <v>-1.1168</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.19</v>
+        <v>-1.1217</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.19</v>
+        <v>-1.1217</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.19</v>
+        <v>-1.1217</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.19</v>
+        <v>-1.1217</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.19</v>
+        <v>-1.1217</v>
       </c>
       <c r="N38" t="n">
         <v>147</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3457</v>
+        <v>-1.2926</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2492</v>
+        <v>-0.2393</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2368</v>
+        <v>-1.1946</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3457</v>
+        <v>-1.2926</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3457</v>
+        <v>-1.2926</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3457</v>
+        <v>-1.2926</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3457</v>
+        <v>-1.2926</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3457</v>
+        <v>-1.2926</v>
       </c>
       <c r="N39" t="n">
         <v>147</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5078</v>
+        <v>-1.4866</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2792</v>
+        <v>-0.2753</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3106</v>
+        <v>-1.283</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5078</v>
+        <v>-1.4866</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5078</v>
+        <v>-1.4866</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5078</v>
+        <v>-1.4866</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5078</v>
+        <v>-1.4866</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5078</v>
+        <v>-1.4866</v>
       </c>
       <c r="N40" t="n">
         <v>152</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9042</v>
+        <v>-1.8191</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3526</v>
+        <v>-0.3368</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.491</v>
+        <v>-1.4345</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9042</v>
+        <v>-1.8191</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9042</v>
+        <v>-1.8191</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9042</v>
+        <v>-1.8191</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9042</v>
+        <v>-1.8191</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9042</v>
+        <v>-1.8191</v>
       </c>
       <c r="N41" t="n">
         <v>147</v>
@@ -2429,10 +2429,10 @@
         <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2095</v>
+        <v>0.1699</v>
       </c>
       <c r="J2" t="n">
-        <v>5.028</v>
+        <v>4.0776</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0422</v>
+        <v>-0.033</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0128</v>
+        <v>-0.792</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0571</v>
+        <v>-0.0464</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.3704</v>
+        <v>-1.1136</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.63</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3947</v>
+        <v>-0.3828</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.472799999999999</v>
+        <v>-9.187200000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.54</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4742</v>
+        <v>-0.4704</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.3808</v>
+        <v>-11.2896</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.296</v>
+        <v>1.3235</v>
       </c>
       <c r="J7" t="n">
-        <v>31.104</v>
+        <v>31.764</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8556</v>
+        <v>0.8386</v>
       </c>
       <c r="J8" t="n">
-        <v>20.5344</v>
+        <v>20.1264</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.27</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6813</v>
+        <v>0.6553</v>
       </c>
       <c r="J9" t="n">
-        <v>16.3512</v>
+        <v>15.7272</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.599</v>
+        <v>0.5703</v>
       </c>
       <c r="J10" t="n">
-        <v>14.376</v>
+        <v>13.6872</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.98</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1498</v>
+        <v>-0.1238</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.5952</v>
+        <v>-2.9712</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8512</v>
+        <v>0.7812</v>
       </c>
       <c r="J12" t="n">
-        <v>15.3216</v>
+        <v>14.0616</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.58</v>
       </c>
       <c r="I13" t="n">
-        <v>0.669</v>
+        <v>0.6004</v>
       </c>
       <c r="J13" t="n">
-        <v>12.042</v>
+        <v>10.8072</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>0.547</v>
+        <v>0.483</v>
       </c>
       <c r="J14" t="n">
-        <v>9.846</v>
+        <v>8.694000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.36</v>
       </c>
       <c r="I15" t="n">
-        <v>0.456</v>
+        <v>0.3967</v>
       </c>
       <c r="J15" t="n">
-        <v>8.208</v>
+        <v>7.1406</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.32</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4134</v>
+        <v>0.3565</v>
       </c>
       <c r="J16" t="n">
-        <v>7.4412</v>
+        <v>6.417</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1412</v>
+        <v>0.1468</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5416</v>
+        <v>2.6424</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2951</v>
+        <v>-0.2824</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.3118</v>
+        <v>-5.0832</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.57</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4274</v>
+        <v>-0.4188</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.6932</v>
+        <v>-7.5384</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.52</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4714</v>
+        <v>-0.4665</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.485200000000001</v>
+        <v>-8.397</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.48</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.1188</v>
+        <v>-9.099</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.26</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5527</v>
+        <v>0.4955</v>
       </c>
       <c r="J22" t="n">
-        <v>16.581</v>
+        <v>14.865</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0948</v>
+        <v>-0.0796</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.844</v>
+        <v>-2.388</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.85</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1955</v>
+        <v>-0.1754</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.865</v>
+        <v>-5.262</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.85</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1955</v>
+        <v>-0.1754</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.865</v>
+        <v>-5.262</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.77</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2756</v>
+        <v>-0.2564</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.268000000000001</v>
+        <v>-7.692</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9797</v>
+        <v>0.9696</v>
       </c>
       <c r="J27" t="n">
-        <v>29.391</v>
+        <v>29.088</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9797</v>
+        <v>0.9696</v>
       </c>
       <c r="J28" t="n">
-        <v>29.391</v>
+        <v>29.088</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3068</v>
+        <v>-0.2654</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.204000000000001</v>
+        <v>-7.962</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3613</v>
+        <v>-0.3188</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.839</v>
+        <v>-9.564</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.439</v>
+        <v>-0.3963</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.17</v>
+        <v>-11.889</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.42</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8649</v>
+        <v>0.8495</v>
       </c>
       <c r="J32" t="n">
-        <v>25.947</v>
+        <v>25.485</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4197</v>
+        <v>0.3817</v>
       </c>
       <c r="J33" t="n">
-        <v>12.591</v>
+        <v>11.451</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1533</v>
+        <v>0.1277</v>
       </c>
       <c r="J34" t="n">
-        <v>4.599</v>
+        <v>3.831</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.99</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0772</v>
+        <v>-0.0568</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.316</v>
+        <v>-1.704</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.189</v>
+        <v>-0.1544</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.67</v>
+        <v>-4.632</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.39</v>
       </c>
       <c r="I37" t="n">
-        <v>0.654</v>
+        <v>0.6231</v>
       </c>
       <c r="J37" t="n">
-        <v>19.62</v>
+        <v>18.693</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.98</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.044</v>
+        <v>-0.0333</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.32</v>
+        <v>-0.999</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0596</v>
+        <v>-0.0466</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.788</v>
+        <v>-1.398</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.91</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1371</v>
+        <v>-0.1178</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.113</v>
+        <v>-3.534</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2033</v>
+        <v>-0.1826</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.099</v>
+        <v>-5.478</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8797</v>
+        <v>0.8649</v>
       </c>
       <c r="J42" t="n">
-        <v>25.5113</v>
+        <v>25.0821</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7815</v>
+        <v>0.767</v>
       </c>
       <c r="J43" t="n">
-        <v>22.6635</v>
+        <v>22.243</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6657</v>
+        <v>0.6542</v>
       </c>
       <c r="J44" t="n">
-        <v>19.3053</v>
+        <v>18.9718</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.27</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6212</v>
+        <v>0.6117</v>
       </c>
       <c r="J45" t="n">
-        <v>18.0148</v>
+        <v>17.7393</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6092</v>
+        <v>-0.5756</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.6668</v>
+        <v>-16.6924</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4631</v>
+        <v>0.4153</v>
       </c>
       <c r="J47" t="n">
-        <v>13.4299</v>
+        <v>12.0437</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2692</v>
+        <v>0.2212</v>
       </c>
       <c r="J48" t="n">
-        <v>7.8068</v>
+        <v>6.4148</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.86</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1839</v>
+        <v>-0.1642</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.3331</v>
+        <v>-4.7618</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.76</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.284</v>
+        <v>-0.2652</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.236000000000001</v>
+        <v>-7.6908</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3588</v>
+        <v>-0.3443</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.4052</v>
+        <v>-9.9847</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5722</v>
+        <v>0.5453</v>
       </c>
       <c r="J52" t="n">
-        <v>17.166</v>
+        <v>16.359</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.07</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1809</v>
+        <v>0.1454</v>
       </c>
       <c r="J53" t="n">
-        <v>5.427</v>
+        <v>4.362</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1809</v>
+        <v>0.1454</v>
       </c>
       <c r="J54" t="n">
-        <v>5.427</v>
+        <v>4.362</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1809</v>
+        <v>0.1454</v>
       </c>
       <c r="J55" t="n">
-        <v>5.427</v>
+        <v>4.362</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.95</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0939</v>
+        <v>-0.0771</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.817</v>
+        <v>-2.313</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.29</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6893</v>
+        <v>0.6742</v>
       </c>
       <c r="J57" t="n">
-        <v>20.679</v>
+        <v>20.226</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.11</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3616</v>
+        <v>0.32</v>
       </c>
       <c r="J58" t="n">
-        <v>10.848</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.93</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2648</v>
+        <v>-0.2255</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.944</v>
+        <v>-6.765</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.91</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3207</v>
+        <v>-0.279</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.621</v>
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3476</v>
+        <v>-0.3052</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.428</v>
+        <v>-9.156000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.28</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5444</v>
+        <v>0.5188</v>
       </c>
       <c r="J62" t="n">
-        <v>14.1544</v>
+        <v>13.4888</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2635</v>
+        <v>0.2157</v>
       </c>
       <c r="J63" t="n">
-        <v>6.851</v>
+        <v>5.6082</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.85</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1966</v>
+        <v>-0.1763</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.1116</v>
+        <v>-4.5838</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2374</v>
+        <v>-0.2173</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.1724</v>
+        <v>-5.6498</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3519</v>
+        <v>-0.3371</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.1494</v>
+        <v>-8.7646</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>0.841</v>
+        <v>0.8258</v>
       </c>
       <c r="J67" t="n">
-        <v>21.866</v>
+        <v>21.4708</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.3</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>17.3628</v>
+        <v>17.0482</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5157</v>
+        <v>0.5068</v>
       </c>
       <c r="J69" t="n">
-        <v>13.4082</v>
+        <v>13.1768</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.14</v>
       </c>
       <c r="I70" t="n">
-        <v>0.406</v>
+        <v>0.3727</v>
       </c>
       <c r="J70" t="n">
-        <v>10.556</v>
+        <v>9.690200000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1956</v>
+        <v>0.1677</v>
       </c>
       <c r="J71" t="n">
-        <v>5.0856</v>
+        <v>4.3602</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.77</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4311</v>
+        <v>1.4583</v>
       </c>
       <c r="J72" t="n">
-        <v>34.3464</v>
+        <v>34.9992</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.55</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1492</v>
+        <v>1.1629</v>
       </c>
       <c r="J73" t="n">
-        <v>27.5808</v>
+        <v>27.9096</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.34</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8137</v>
+        <v>0.7956</v>
       </c>
       <c r="J74" t="n">
-        <v>19.5288</v>
+        <v>19.0944</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.05</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1501</v>
+        <v>0.1238</v>
       </c>
       <c r="J75" t="n">
-        <v>3.6024</v>
+        <v>2.9712</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.87</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4766</v>
+        <v>-0.4397</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.4384</v>
+        <v>-10.5528</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.18</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4213</v>
+        <v>0.3656</v>
       </c>
       <c r="J77" t="n">
-        <v>10.1112</v>
+        <v>8.7744</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4033</v>
+        <v>0.3482</v>
       </c>
       <c r="J78" t="n">
-        <v>9.6792</v>
+        <v>8.3568</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.77</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2738</v>
+        <v>-0.2547</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.5712</v>
+        <v>-6.1128</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.76</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2834</v>
+        <v>-0.2646</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.8016</v>
+        <v>-6.3504</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3398</v>
+        <v>-0.324</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.155200000000001</v>
+        <v>-7.776</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.92</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0013</v>
+        <v>0.0837</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0234</v>
+        <v>1.5066</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.54</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.4288</v>
+        <v>-0.4271</v>
       </c>
       <c r="J83" t="n">
-        <v>-7.7184</v>
+        <v>-7.6878</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.47</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.4883</v>
+        <v>-0.4887</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.789400000000001</v>
+        <v>-8.7966</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.25</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.6863</v>
+        <v>-0.7114</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.3534</v>
+        <v>-12.8052</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.25</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6863</v>
+        <v>-0.7114</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.3534</v>
+        <v>-12.8052</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>2.07</v>
       </c>
       <c r="I87" t="n">
-        <v>1.7165</v>
+        <v>1.766</v>
       </c>
       <c r="J87" t="n">
-        <v>30.897</v>
+        <v>31.788</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.9</v>
       </c>
       <c r="I88" t="n">
-        <v>1.5248</v>
+        <v>1.5609</v>
       </c>
       <c r="J88" t="n">
-        <v>27.4464</v>
+        <v>28.0962</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.74</v>
       </c>
       <c r="I89" t="n">
-        <v>1.3402</v>
+        <v>1.3682</v>
       </c>
       <c r="J89" t="n">
-        <v>24.1236</v>
+        <v>24.6276</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.52</v>
       </c>
       <c r="I90" t="n">
-        <v>1.0742</v>
+        <v>1.0959</v>
       </c>
       <c r="J90" t="n">
-        <v>19.3356</v>
+        <v>19.7262</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.18</v>
       </c>
       <c r="I91" t="n">
-        <v>0.4341</v>
+        <v>0.4003</v>
       </c>
       <c r="J91" t="n">
-        <v>7.8138</v>
+        <v>7.2054</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.38</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8995</v>
+        <v>0.8842</v>
       </c>
       <c r="J92" t="n">
-        <v>23.387</v>
+        <v>22.9892</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.27</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6839</v>
+        <v>0.6564</v>
       </c>
       <c r="J93" t="n">
-        <v>17.7814</v>
+        <v>17.0664</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.23</v>
       </c>
       <c r="I94" t="n">
-        <v>0.603</v>
+        <v>0.5729</v>
       </c>
       <c r="J94" t="n">
-        <v>15.678</v>
+        <v>14.8954</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.21</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5605</v>
+        <v>0.5295</v>
       </c>
       <c r="J95" t="n">
-        <v>14.573</v>
+        <v>13.767</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.19</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5168</v>
+        <v>0.4849</v>
       </c>
       <c r="J96" t="n">
-        <v>13.4368</v>
+        <v>12.6074</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.09</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2817</v>
+        <v>0.2372</v>
       </c>
       <c r="J97" t="n">
-        <v>7.3242</v>
+        <v>6.1672</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.89</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1427</v>
+        <v>-0.127</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.7102</v>
+        <v>-3.302</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2256</v>
+        <v>-0.2079</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.8656</v>
+        <v>-5.4054</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.71</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3199</v>
+        <v>-0.3033</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.317399999999999</v>
+        <v>-7.8858</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.57</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.446</v>
+        <v>-0.4389</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.596</v>
+        <v>-11.4114</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6606</v>
+        <v>0.6268</v>
       </c>
       <c r="J102" t="n">
-        <v>18.4968</v>
+        <v>17.5504</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.18</v>
       </c>
       <c r="I103" t="n">
-        <v>0.508</v>
+        <v>0.4704</v>
       </c>
       <c r="J103" t="n">
-        <v>14.224</v>
+        <v>13.1712</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.15</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4399</v>
+        <v>0.4025</v>
       </c>
       <c r="J104" t="n">
-        <v>12.3172</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.319</v>
+        <v>0.2842</v>
       </c>
       <c r="J105" t="n">
-        <v>8.932</v>
+        <v>7.9576</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.04</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1475</v>
+        <v>0.1229</v>
       </c>
       <c r="J106" t="n">
-        <v>4.13</v>
+        <v>3.4412</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.07</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2093</v>
+        <v>0.1669</v>
       </c>
       <c r="J107" t="n">
-        <v>5.8604</v>
+        <v>4.6732</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.99</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0186</v>
+        <v>-0.0137</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.5208</v>
+        <v>-0.3836</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1831</v>
+        <v>-0.1635</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.1268</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2141</v>
+        <v>-0.1941</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.9948</v>
+        <v>-5.4348</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2342</v>
+        <v>-0.2143</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.5576</v>
+        <v>-6.0004</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.184</v>
+        <v>0.1444</v>
       </c>
       <c r="J112" t="n">
-        <v>4.784</v>
+        <v>3.7544</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0098</v>
+        <v>0.0063</v>
       </c>
       <c r="J113" t="n">
-        <v>0.2548</v>
+        <v>0.1638</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0815</v>
+        <v>-0.0678</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.119</v>
+        <v>-1.7628</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1296</v>
+        <v>-0.112</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.3696</v>
+        <v>-2.912</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.71</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3315</v>
+        <v>-0.3152</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.619</v>
+        <v>-8.1952</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.37</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8988</v>
+        <v>0.8811</v>
       </c>
       <c r="J117" t="n">
-        <v>23.3688</v>
+        <v>22.9086</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6551</v>
+        <v>0.6222</v>
       </c>
       <c r="J118" t="n">
-        <v>17.0326</v>
+        <v>16.1772</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5914</v>
+        <v>0.5566</v>
       </c>
       <c r="J119" t="n">
-        <v>15.3764</v>
+        <v>14.4716</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2334</v>
+        <v>0.2031</v>
       </c>
       <c r="J120" t="n">
-        <v>6.0684</v>
+        <v>5.2806</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2323</v>
+        <v>-0.1954</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.0398</v>
+        <v>-5.0804</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4842</v>
+        <v>0.4254</v>
       </c>
       <c r="J122" t="n">
-        <v>14.526</v>
+        <v>12.762</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4507</v>
+        <v>0.3927</v>
       </c>
       <c r="J123" t="n">
-        <v>13.521</v>
+        <v>11.781</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.04</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1246</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J124" t="n">
-        <v>3.738</v>
+        <v>2.826</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.92</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1236</v>
+        <v>-0.1051</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.708</v>
+        <v>-3.153</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4372</v>
+        <v>-0.431</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.116</v>
+        <v>-12.93</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.63</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3107</v>
+        <v>1.3357</v>
       </c>
       <c r="J127" t="n">
-        <v>39.321</v>
+        <v>40.071</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.217</v>
+        <v>0.1856</v>
       </c>
       <c r="J128" t="n">
-        <v>6.51</v>
+        <v>5.568</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1157</v>
+        <v>-0.089</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.471</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2483</v>
+        <v>-0.2095</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.449</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4632</v>
+        <v>-0.4209</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.896</v>
+        <v>-12.627</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>0.945</v>
+        <v>0.9325</v>
       </c>
       <c r="J132" t="n">
-        <v>24.57</v>
+        <v>24.245</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.26</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6822</v>
+        <v>0.6492</v>
       </c>
       <c r="J133" t="n">
-        <v>17.7372</v>
+        <v>16.8792</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.13</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3937</v>
+        <v>0.3568</v>
       </c>
       <c r="J134" t="n">
-        <v>10.2362</v>
+        <v>9.2768</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1478</v>
+        <v>0.1232</v>
       </c>
       <c r="J135" t="n">
-        <v>3.8428</v>
+        <v>3.2032</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.396</v>
+        <v>-0.3538</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.296</v>
+        <v>-9.1988</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3032</v>
+        <v>0.2541</v>
       </c>
       <c r="J137" t="n">
-        <v>7.8832</v>
+        <v>6.6066</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1975</v>
+        <v>0.1573</v>
       </c>
       <c r="J138" t="n">
-        <v>5.135</v>
+        <v>4.0898</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.83</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2105</v>
+        <v>-0.1912</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.473</v>
+        <v>-4.9712</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.78</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2598</v>
+        <v>-0.2407</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.7548</v>
+        <v>-6.2582</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4432</v>
+        <v>-0.4363</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.5232</v>
+        <v>-11.3438</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.53</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1499</v>
+        <v>1.1632</v>
       </c>
       <c r="J142" t="n">
-        <v>31.0473</v>
+        <v>31.4064</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.39</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9351</v>
+        <v>0.9216</v>
       </c>
       <c r="J143" t="n">
-        <v>25.2477</v>
+        <v>24.8832</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4128</v>
+        <v>0.3775</v>
       </c>
       <c r="J144" t="n">
-        <v>11.1456</v>
+        <v>10.1925</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0711</v>
+        <v>0.0549</v>
       </c>
       <c r="J145" t="n">
-        <v>1.9197</v>
+        <v>1.4823</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5755</v>
+        <v>-0.5385</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.5385</v>
+        <v>-14.5395</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5506</v>
+        <v>0.4956</v>
       </c>
       <c r="J147" t="n">
-        <v>14.8662</v>
+        <v>13.3812</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1197</v>
+        <v>0.0896</v>
       </c>
       <c r="J148" t="n">
-        <v>3.2319</v>
+        <v>2.4192</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2323</v>
+        <v>-0.2126</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.2721</v>
+        <v>-5.7402</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2422</v>
+        <v>-0.2226</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.5394</v>
+        <v>-6.0102</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4539</v>
+        <v>-0.4484</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.2553</v>
+        <v>-12.1068</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1059</v>
+        <v>-0.0917</v>
       </c>
       <c r="J152" t="n">
-        <v>-3.0711</v>
+        <v>-2.6593</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.86</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1745</v>
+        <v>-0.1581</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.0605</v>
+        <v>-4.5849</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.86</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1745</v>
+        <v>-0.1581</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.0605</v>
+        <v>-4.5849</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2056</v>
+        <v>-0.1885</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.9624</v>
+        <v>-5.4665</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4625</v>
+        <v>-0.4571</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.4125</v>
+        <v>-13.2559</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.67</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3112</v>
+        <v>1.3311</v>
       </c>
       <c r="J157" t="n">
-        <v>38.0248</v>
+        <v>38.6019</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0741</v>
+        <v>1.0837</v>
       </c>
       <c r="J158" t="n">
-        <v>31.1489</v>
+        <v>31.4273</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.39</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8999</v>
       </c>
       <c r="J159" t="n">
-        <v>26.4712</v>
+        <v>26.0971</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1852</v>
+        <v>0.1575</v>
       </c>
       <c r="J160" t="n">
-        <v>5.3708</v>
+        <v>4.5675</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.82</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5928</v>
+        <v>-0.5596</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.1912</v>
+        <v>-16.2284</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.73</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3479</v>
+        <v>1.3714</v>
       </c>
       <c r="J162" t="n">
-        <v>28.3059</v>
+        <v>28.7994</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.64</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2376</v>
+        <v>1.2574</v>
       </c>
       <c r="J163" t="n">
-        <v>25.9896</v>
+        <v>26.4054</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.61</v>
       </c>
       <c r="I164" t="n">
-        <v>1.2004</v>
+        <v>1.2194</v>
       </c>
       <c r="J164" t="n">
-        <v>25.2084</v>
+        <v>25.6074</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.58</v>
       </c>
       <c r="I165" t="n">
-        <v>1.163</v>
+        <v>1.1814</v>
       </c>
       <c r="J165" t="n">
-        <v>24.423</v>
+        <v>24.8094</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.95</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2834</v>
+        <v>-0.2547</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.9514</v>
+        <v>-5.3487</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.83</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.1782</v>
+        <v>-0.1614</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.7422</v>
+        <v>-3.3894</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.74</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2723</v>
+        <v>-0.2593</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.7183</v>
+        <v>-5.4453</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.67</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3383</v>
+        <v>-0.3273</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.1043</v>
+        <v>-6.8733</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.52</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4686</v>
+        <v>-0.4636</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.8406</v>
+        <v>-9.7356</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.45</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5302</v>
+        <v>-0.5319</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.1342</v>
+        <v>-11.1699</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.85</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1452</v>
+        <v>-0.1252</v>
       </c>
       <c r="J172" t="n">
-        <v>-2.4684</v>
+        <v>-2.1284</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.78</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2231</v>
+        <v>-0.2076</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.7927</v>
+        <v>-3.5292</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.54</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4459</v>
+        <v>-0.4397</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.5803</v>
+        <v>-7.4749</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4722</v>
+        <v>-0.4679</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.0274</v>
+        <v>-7.9543</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.35</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6132</v>
+        <v>-0.6268</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.4244</v>
+        <v>-10.6556</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.83</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4688</v>
+        <v>1.4985</v>
       </c>
       <c r="J177" t="n">
-        <v>24.9696</v>
+        <v>25.4745</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.67</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2751</v>
+        <v>1.2958</v>
       </c>
       <c r="J178" t="n">
-        <v>21.6767</v>
+        <v>22.0286</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.46</v>
       </c>
       <c r="I179" t="n">
-        <v>1.007</v>
+        <v>1.0158</v>
       </c>
       <c r="J179" t="n">
-        <v>17.119</v>
+        <v>17.2686</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.45</v>
       </c>
       <c r="I180" t="n">
-        <v>0.9916</v>
+        <v>0.9984</v>
       </c>
       <c r="J180" t="n">
-        <v>16.8572</v>
+        <v>16.9728</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.08</v>
       </c>
       <c r="I181" t="n">
-        <v>0.2102</v>
+        <v>0.1772</v>
       </c>
       <c r="J181" t="n">
-        <v>3.5734</v>
+        <v>3.0124</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.46</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8811</v>
+        <v>0.844</v>
       </c>
       <c r="J182" t="n">
-        <v>25.5519</v>
+        <v>24.476</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2337</v>
+        <v>0.1891</v>
       </c>
       <c r="J183" t="n">
-        <v>6.7773</v>
+        <v>5.4839</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.74</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3009</v>
+        <v>-0.2828</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.726100000000001</v>
+        <v>-8.2012</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.7</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3382</v>
+        <v>-0.3222</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.8078</v>
+        <v>-9.3438</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4979</v>
+        <v>-0.498</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.4391</v>
+        <v>-14.442</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.48</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0655</v>
+        <v>1.0736</v>
       </c>
       <c r="J187" t="n">
-        <v>30.8995</v>
+        <v>31.1344</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.47</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0512</v>
+        <v>1.0574</v>
       </c>
       <c r="J188" t="n">
-        <v>30.4848</v>
+        <v>30.6646</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.35</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8417</v>
+        <v>0.8223</v>
       </c>
       <c r="J189" t="n">
-        <v>24.4093</v>
+        <v>23.8467</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.35</v>
       </c>
       <c r="I190" t="n">
-        <v>0.8417</v>
+        <v>0.8223</v>
       </c>
       <c r="J190" t="n">
-        <v>24.4093</v>
+        <v>23.8467</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-1.0009</v>
       </c>
       <c r="J191" t="n">
-        <v>-28.9275</v>
+        <v>-29.0261</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.3</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6223</v>
+        <v>0.5671</v>
       </c>
       <c r="J192" t="n">
-        <v>16.1798</v>
+        <v>14.7446</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3466</v>
+        <v>0.2935</v>
       </c>
       <c r="J193" t="n">
-        <v>9.0116</v>
+        <v>7.631</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.08</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2282</v>
+        <v>0.1838</v>
       </c>
       <c r="J194" t="n">
-        <v>5.9332</v>
+        <v>4.7788</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.66</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3769</v>
+        <v>-0.3639</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.7994</v>
+        <v>-9.461399999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.43</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5759</v>
+        <v>-0.5879</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.9734</v>
+        <v>-15.2854</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.95</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6626</v>
+        <v>1.7118</v>
       </c>
       <c r="J197" t="n">
-        <v>43.2276</v>
+        <v>44.5068</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.4</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9323</v>
+        <v>0.9212</v>
       </c>
       <c r="J198" t="n">
-        <v>24.2398</v>
+        <v>23.9512</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.14</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3975</v>
+        <v>0.3652</v>
       </c>
       <c r="J199" t="n">
-        <v>10.335</v>
+        <v>9.495200000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.0472</v>
+        <v>-0.0423</v>
       </c>
       <c r="J200" t="n">
-        <v>-1.2272</v>
+        <v>-1.0998</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3667</v>
+        <v>-0.3279</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.5342</v>
+        <v>-8.525399999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.59</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2073</v>
+        <v>1.2224</v>
       </c>
       <c r="J202" t="n">
-        <v>25.3533</v>
+        <v>25.6704</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.894</v>
+        <v>0.8796</v>
       </c>
       <c r="J203" t="n">
-        <v>18.774</v>
+        <v>18.4716</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.27</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6815</v>
+        <v>0.6554</v>
       </c>
       <c r="J204" t="n">
-        <v>14.3115</v>
+        <v>13.7634</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.2</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5346</v>
+        <v>0.5041</v>
       </c>
       <c r="J205" t="n">
-        <v>11.2266</v>
+        <v>10.5861</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.99</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1081</v>
+        <v>-0.0881</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.2701</v>
+        <v>-1.8501</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.01</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1114</v>
+        <v>0.0954</v>
       </c>
       <c r="J207" t="n">
-        <v>2.3394</v>
+        <v>2.0034</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1862</v>
+        <v>-0.1706</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.9102</v>
+        <v>-3.5826</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.76</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2665</v>
+        <v>-0.2512</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.5965</v>
+        <v>-5.2752</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.74</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2849</v>
+        <v>-0.2696</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.9829</v>
+        <v>-5.6616</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.32</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.653</v>
+        <v>-0.676</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.713</v>
+        <v>-14.196</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.48</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8709</v>
+        <v>0.8245</v>
       </c>
       <c r="J212" t="n">
-        <v>24.3852</v>
+        <v>23.086</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1922</v>
+        <v>0.1522</v>
       </c>
       <c r="J213" t="n">
-        <v>5.3816</v>
+        <v>4.2616</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1005</v>
+        <v>0.0742</v>
       </c>
       <c r="J214" t="n">
-        <v>2.814</v>
+        <v>2.0776</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.84</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2115</v>
+        <v>-0.1909</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.922</v>
+        <v>-5.3452</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4716</v>
+        <v>-0.4694</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.2048</v>
+        <v>-13.1432</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.36</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8832</v>
+        <v>0.8638</v>
       </c>
       <c r="J217" t="n">
-        <v>24.7296</v>
+        <v>24.1864</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.29</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7416</v>
+        <v>0.7123</v>
       </c>
       <c r="J218" t="n">
-        <v>20.7648</v>
+        <v>19.9444</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.11</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3427</v>
+        <v>0.3077</v>
       </c>
       <c r="J219" t="n">
-        <v>9.595599999999999</v>
+        <v>8.615600000000001</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.1</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3172</v>
+        <v>0.2829</v>
       </c>
       <c r="J220" t="n">
-        <v>8.881600000000001</v>
+        <v>7.9212</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.92</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3176</v>
+        <v>-0.2767</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.892799999999999</v>
+        <v>-7.7476</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.93</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.0814</v>
+        <v>-0.0672</v>
       </c>
       <c r="J222" t="n">
-        <v>-1.7094</v>
+        <v>-1.4112</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.76</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2669</v>
+        <v>-0.2515</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.6049</v>
+        <v>-5.2815</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.71</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3118</v>
+        <v>-0.2966</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.5478</v>
+        <v>-6.2286</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.7</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3208</v>
+        <v>-0.3058</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.7368</v>
+        <v>-6.4218</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.59</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4195</v>
+        <v>-0.4097</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.8095</v>
+        <v>-8.6037</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.92</v>
       </c>
       <c r="I227" t="n">
-        <v>1.5802</v>
+        <v>1.6177</v>
       </c>
       <c r="J227" t="n">
-        <v>33.1842</v>
+        <v>33.9717</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.56</v>
       </c>
       <c r="I228" t="n">
-        <v>1.1409</v>
+        <v>1.158</v>
       </c>
       <c r="J228" t="n">
-        <v>23.9589</v>
+        <v>24.318</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.42</v>
       </c>
       <c r="I229" t="n">
-        <v>0.9449</v>
+        <v>0.9445</v>
       </c>
       <c r="J229" t="n">
-        <v>19.8429</v>
+        <v>19.8345</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.36</v>
       </c>
       <c r="I230" t="n">
-        <v>0.8346</v>
+        <v>0.8248</v>
       </c>
       <c r="J230" t="n">
-        <v>17.5266</v>
+        <v>17.3208</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.1</v>
       </c>
       <c r="I231" t="n">
-        <v>0.2677</v>
+        <v>0.2344</v>
       </c>
       <c r="J231" t="n">
-        <v>5.6217</v>
+        <v>4.9224</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.46</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8375</v>
+        <v>0.7879</v>
       </c>
       <c r="J232" t="n">
-        <v>25.125</v>
+        <v>23.637</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0827</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.988</v>
+        <v>-2.481</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1243</v>
+        <v>-0.1057</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.729</v>
+        <v>-3.171</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.87</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1809</v>
+        <v>-0.1604</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.427</v>
+        <v>-4.812</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2022</v>
+        <v>-0.1815</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.066</v>
+        <v>-5.445</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.32</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8166</v>
+        <v>0.7913</v>
       </c>
       <c r="J237" t="n">
-        <v>24.498</v>
+        <v>23.739</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.29</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7544</v>
+        <v>0.7246</v>
       </c>
       <c r="J238" t="n">
-        <v>22.632</v>
+        <v>21.738</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.1</v>
       </c>
       <c r="I239" t="n">
-        <v>0.324</v>
+        <v>0.2871</v>
       </c>
       <c r="J239" t="n">
-        <v>9.720000000000001</v>
+        <v>8.613</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2502</v>
+        <v>-0.2113</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.506</v>
+        <v>-6.339</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.87</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4402</v>
+        <v>-0.3976</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.206</v>
+        <v>-11.928</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3104</v>
+        <v>0.266</v>
       </c>
       <c r="J242" t="n">
-        <v>7.1392</v>
+        <v>6.118</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.86</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1733</v>
+        <v>-0.1571</v>
       </c>
       <c r="J243" t="n">
-        <v>-3.9859</v>
+        <v>-3.6133</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.74</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2899</v>
+        <v>-0.2728</v>
       </c>
       <c r="J244" t="n">
-        <v>-6.6677</v>
+        <v>-6.2744</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.66</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3634</v>
+        <v>-0.3492</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.3582</v>
+        <v>-8.031599999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.61</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4083</v>
+        <v>-0.3975</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.3909</v>
+        <v>-9.1425</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.63</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2486</v>
+        <v>1.2657</v>
       </c>
       <c r="J247" t="n">
-        <v>28.7178</v>
+        <v>29.1111</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.56</v>
       </c>
       <c r="I248" t="n">
-        <v>1.158</v>
+        <v>1.1723</v>
       </c>
       <c r="J248" t="n">
-        <v>26.634</v>
+        <v>26.9629</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.31</v>
       </c>
       <c r="I249" t="n">
-        <v>0.7544</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J249" t="n">
-        <v>17.3512</v>
+        <v>16.8912</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.15</v>
       </c>
       <c r="I250" t="n">
-        <v>0.4118</v>
+        <v>0.3802</v>
       </c>
       <c r="J250" t="n">
-        <v>9.471399999999999</v>
+        <v>8.7446</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.06</v>
       </c>
       <c r="I251" t="n">
-        <v>0.1762</v>
+        <v>0.148</v>
       </c>
       <c r="J251" t="n">
-        <v>4.0526</v>
+        <v>3.404</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.11</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2912</v>
+        <v>0.2416</v>
       </c>
       <c r="J252" t="n">
-        <v>7.5712</v>
+        <v>6.2816</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.08</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2302</v>
+        <v>0.1856</v>
       </c>
       <c r="J253" t="n">
-        <v>5.9852</v>
+        <v>4.8256</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.86</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1832</v>
+        <v>-0.1636</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.7632</v>
+        <v>-4.2536</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.78</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2639</v>
+        <v>-0.2445</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.8614</v>
+        <v>-6.357</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.74</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3023</v>
+        <v>-0.2843</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.8598</v>
+        <v>-7.3918</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.51</v>
       </c>
       <c r="I257" t="n">
-        <v>1.1108</v>
+        <v>1.1226</v>
       </c>
       <c r="J257" t="n">
-        <v>28.8808</v>
+        <v>29.1876</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.41</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9593</v>
+        <v>0.9503</v>
       </c>
       <c r="J258" t="n">
-        <v>24.9418</v>
+        <v>24.7078</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.14</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4048</v>
+        <v>0.3714</v>
       </c>
       <c r="J259" t="n">
-        <v>10.5248</v>
+        <v>9.6564</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2782</v>
+        <v>0.2468</v>
       </c>
       <c r="J260" t="n">
-        <v>7.2332</v>
+        <v>6.4168</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.02</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0618</v>
+        <v>0.0456</v>
       </c>
       <c r="J261" t="n">
-        <v>1.6068</v>
+        <v>1.1856</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.69</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3833</v>
+        <v>1.413</v>
       </c>
       <c r="J262" t="n">
-        <v>30.4326</v>
+        <v>31.086</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.29</v>
       </c>
       <c r="I263" t="n">
-        <v>0.7507</v>
+        <v>0.7209</v>
       </c>
       <c r="J263" t="n">
-        <v>16.5154</v>
+        <v>15.8598</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2528</v>
+        <v>-0.2139</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.5616</v>
+        <v>-4.7058</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.85</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4924</v>
+        <v>-0.451</v>
       </c>
       <c r="J265" t="n">
-        <v>-10.8328</v>
+        <v>-9.922000000000001</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.82</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5643</v>
+        <v>-0.5255</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.4146</v>
+        <v>-11.561</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.21</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4753</v>
+        <v>0.4189</v>
       </c>
       <c r="J267" t="n">
-        <v>10.4566</v>
+        <v>9.2158</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.87</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1725</v>
+        <v>-0.1532</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.795</v>
+        <v>-3.3704</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2038</v>
+        <v>-0.1839</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.4836</v>
+        <v>-4.0458</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.82</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2242</v>
+        <v>-0.2042</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.9324</v>
+        <v>-4.4924</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.82</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2242</v>
+        <v>-0.2042</v>
       </c>
       <c r="J271" t="n">
-        <v>-4.9324</v>
+        <v>-4.4924</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5022</v>
+        <v>0.4433</v>
       </c>
       <c r="J272" t="n">
-        <v>15.066</v>
+        <v>13.299</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.13</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3108</v>
+        <v>0.2594</v>
       </c>
       <c r="J273" t="n">
-        <v>9.324</v>
+        <v>7.782</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.04</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1254</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J274" t="n">
-        <v>3.762</v>
+        <v>2.841</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.85</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2009</v>
+        <v>-0.1803</v>
       </c>
       <c r="J275" t="n">
-        <v>-6.027</v>
+        <v>-5.409</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3379</v>
+        <v>-0.3224</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.137</v>
+        <v>-9.672000000000001</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.29</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5582</v>
+        <v>0.4985</v>
       </c>
       <c r="J277" t="n">
-        <v>16.746</v>
+        <v>14.955</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.18</v>
       </c>
       <c r="I278" t="n">
-        <v>0.381</v>
+        <v>0.327</v>
       </c>
       <c r="J278" t="n">
-        <v>11.43</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2762</v>
+        <v>0.2302</v>
       </c>
       <c r="J279" t="n">
-        <v>8.286</v>
+        <v>6.906</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.03</v>
       </c>
       <c r="I280" t="n">
-        <v>0.09</v>
+        <v>0.0682</v>
       </c>
       <c r="J280" t="n">
-        <v>2.7</v>
+        <v>2.046</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.87</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.1886</v>
+        <v>-0.1682</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.658</v>
+        <v>-5.046</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.12</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3358</v>
+        <v>0.287</v>
       </c>
       <c r="J282" t="n">
-        <v>8.395</v>
+        <v>7.175</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.11</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3158</v>
+        <v>0.268</v>
       </c>
       <c r="J283" t="n">
-        <v>7.895</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.77</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2656</v>
+        <v>-0.2472</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.64</v>
+        <v>-6.18</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.6</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4217</v>
+        <v>-0.4122</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.5425</v>
+        <v>-10.305</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.57</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4481</v>
+        <v>-0.4414</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.2025</v>
+        <v>-11.035</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.59</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2016</v>
+        <v>1.2168</v>
       </c>
       <c r="J287" t="n">
-        <v>30.04</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.33</v>
       </c>
       <c r="I288" t="n">
-        <v>0.7947</v>
+        <v>0.7755</v>
       </c>
       <c r="J288" t="n">
-        <v>19.8675</v>
+        <v>19.3875</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.31</v>
       </c>
       <c r="I289" t="n">
-        <v>0.7569</v>
+        <v>0.7357</v>
       </c>
       <c r="J289" t="n">
-        <v>18.9225</v>
+        <v>18.3925</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.31</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7569</v>
+        <v>0.7357</v>
       </c>
       <c r="J290" t="n">
-        <v>18.9225</v>
+        <v>18.3925</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.04</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1184</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>2.96</v>
+        <v>2.3575</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.49</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0711</v>
+        <v>1.0808</v>
       </c>
       <c r="J292" t="n">
-        <v>26.7775</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.34</v>
       </c>
       <c r="I293" t="n">
-        <v>0.8151</v>
+        <v>0.7964</v>
       </c>
       <c r="J293" t="n">
-        <v>20.3775</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.31</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7577</v>
+        <v>0.736</v>
       </c>
       <c r="J294" t="n">
-        <v>18.9425</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.26</v>
       </c>
       <c r="I295" t="n">
-        <v>0.6592</v>
+        <v>0.6333</v>
       </c>
       <c r="J295" t="n">
-        <v>16.48</v>
+        <v>15.8325</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.12</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3445</v>
+        <v>0.3125</v>
       </c>
       <c r="J296" t="n">
-        <v>8.612500000000001</v>
+        <v>7.8125</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.07</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2301</v>
+        <v>0.1881</v>
       </c>
       <c r="J297" t="n">
-        <v>5.7525</v>
+        <v>4.7025</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.92</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1105</v>
+        <v>-0.0959</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.7625</v>
+        <v>-2.3975</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2371</v>
+        <v>-0.2185</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.9275</v>
+        <v>-5.4625</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.72</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3132</v>
+        <v>-0.2961</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.83</v>
+        <v>-7.4025</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.68</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3501</v>
+        <v>-0.3349</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.7525</v>
+        <v>-8.3725</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.51</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1043</v>
+        <v>1.1161</v>
       </c>
       <c r="J302" t="n">
-        <v>27.6075</v>
+        <v>27.9025</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.49</v>
       </c>
       <c r="I303" t="n">
-        <v>1.0772</v>
+        <v>1.0869</v>
       </c>
       <c r="J303" t="n">
-        <v>26.93</v>
+        <v>27.1725</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.32</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7813</v>
+        <v>0.7588</v>
       </c>
       <c r="J304" t="n">
-        <v>19.5325</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.1</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2991</v>
+        <v>0.2675</v>
       </c>
       <c r="J305" t="n">
-        <v>7.4775</v>
+        <v>6.6875</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.92</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3371</v>
+        <v>-0.2984</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.4275</v>
+        <v>-7.46</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.06</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2045</v>
+        <v>0.1645</v>
       </c>
       <c r="J307" t="n">
-        <v>5.1125</v>
+        <v>4.1125</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.97</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0445</v>
+        <v>-0.0353</v>
       </c>
       <c r="J308" t="n">
-        <v>-1.1125</v>
+        <v>-0.8825</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0866</v>
+        <v>-0.0735</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.165</v>
+        <v>-1.8375</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.65</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3784</v>
+        <v>-0.3652</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.62</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4054</v>
+        <v>-0.3944</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.135</v>
+        <v>-9.859999999999999</v>
       </c>
     </row>
   </sheetData>
